--- a/raw/Timetable_2026Autumn_2025DT.xlsx
+++ b/raw/Timetable_2026Autumn_2025DT.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30425"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="48" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C0F2A57-2830-488F-89B0-351B91B0C553}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60E3F130-AF85-4002-A48C-13207D71512B}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="186">
   <si>
     <t>week</t>
   </si>
@@ -603,9 +603,6 @@
   </si>
   <si>
     <t>B209</t>
-  </si>
-  <si>
-    <t>B409</t>
   </si>
 </sst>
 </file>
@@ -1035,7 +1032,58 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1045,9 +1093,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1077,57 +1122,9 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -1473,81 +1470,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="65"/>
+      <c r="D2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73" t="s">
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73" t="s">
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73" t="s">
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73" t="s">
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="73"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="74" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="73" t="s">
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73" t="s">
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73" t="s">
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73" t="s">
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="54">
+      <c r="A4" s="52">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -1605,7 +1602,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="54"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -1669,7 +1666,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="54"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
@@ -1733,7 +1730,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="54"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
@@ -1795,7 +1792,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="54"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
@@ -1841,7 +1838,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="54"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
@@ -1883,7 +1880,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="54"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
@@ -1927,7 +1924,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="50">
+      <c r="A11" s="62">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -1991,7 +1988,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="50"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="11" t="s">
         <v>48</v>
       </c>
@@ -2007,7 +2004,7 @@
       <c r="F12" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="79" t="s">
+      <c r="G12" s="50" t="s">
         <v>25</v>
       </c>
       <c r="H12" s="13" t="s">
@@ -2053,7 +2050,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="50"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="11" t="s">
         <v>49</v>
       </c>
@@ -2105,7 +2102,7 @@
       <c r="AA13" s="10"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="50"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="11" t="s">
         <v>50</v>
       </c>
@@ -2169,7 +2166,7 @@
       <c r="AA14" s="10"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="50"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="11" t="s">
         <v>54</v>
       </c>
@@ -2198,7 +2195,7 @@
       <c r="U15" s="14"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="50"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="11" t="s">
         <v>55</v>
       </c>
@@ -2225,7 +2222,7 @@
       <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="50"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="11" t="s">
         <v>56</v>
       </c>
@@ -2252,7 +2249,7 @@
       <c r="U17" s="14"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="54">
+      <c r="A18" s="52">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -2301,7 +2298,7 @@
       <c r="U18" s="5"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="54"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
@@ -2348,7 +2345,7 @@
       <c r="U19" s="5"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="54"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
@@ -2395,7 +2392,7 @@
       <c r="U20" s="5"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="54"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
@@ -2454,7 +2451,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="54"/>
+      <c r="A22" s="52"/>
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -2483,7 +2480,7 @@
       <c r="U22" s="5"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="54"/>
+      <c r="A23" s="52"/>
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -2510,7 +2507,7 @@
       <c r="U23" s="5"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="54"/>
+      <c r="A24" s="52"/>
       <c r="B24" s="16" t="s">
         <v>63</v>
       </c>
@@ -2537,7 +2534,7 @@
       <c r="U24" s="19"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="50">
+      <c r="A25" s="62">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -2586,7 +2583,7 @@
       <c r="U25" s="14"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="50"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="11" t="s">
         <v>65</v>
       </c>
@@ -2602,7 +2599,7 @@
       <c r="F26" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G26" s="79" t="s">
+      <c r="G26" s="50" t="s">
         <v>25</v>
       </c>
       <c r="H26" s="13" t="s">
@@ -2633,7 +2630,7 @@
       <c r="U26" s="14"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="50"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="11" t="s">
         <v>66</v>
       </c>
@@ -2680,7 +2677,7 @@
       <c r="U27" s="14"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="50"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="11" t="s">
         <v>67</v>
       </c>
@@ -2727,90 +2724,90 @@
       <c r="U28" s="14"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="50"/>
+      <c r="A29" s="62"/>
       <c r="B29" s="23" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="64" t="s">
+      <c r="D29" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="66"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="55"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="50"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="23" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="67"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
-      <c r="M30" s="68"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="68"/>
-      <c r="P30" s="68"/>
-      <c r="Q30" s="68"/>
-      <c r="R30" s="68"/>
-      <c r="S30" s="68"/>
-      <c r="T30" s="68"/>
-      <c r="U30" s="69"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="58"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="50"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="23" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="70"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="72"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="54">
+      <c r="A32" s="52">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2859,7 +2856,7 @@
       <c r="U32" s="5"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="54"/>
+      <c r="A33" s="52"/>
       <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
@@ -2906,7 +2903,7 @@
       <c r="U33" s="5"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="54"/>
+      <c r="A34" s="52"/>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
@@ -2953,117 +2950,117 @@
       <c r="U34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="54"/>
+      <c r="A35" s="52"/>
       <c r="B35" s="25" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="64" t="s">
+      <c r="D35" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="65"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="66"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="54"/>
+      <c r="A36" s="52"/>
       <c r="B36" s="25" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="68"/>
-      <c r="M36" s="68"/>
-      <c r="N36" s="68"/>
-      <c r="O36" s="68"/>
-      <c r="P36" s="68"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="68"/>
-      <c r="T36" s="68"/>
-      <c r="U36" s="69"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="57"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="58"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="54"/>
+      <c r="A37" s="52"/>
       <c r="B37" s="25" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
-      <c r="L37" s="68"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="68"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="68"/>
-      <c r="Q37" s="68"/>
-      <c r="R37" s="68"/>
-      <c r="S37" s="68"/>
-      <c r="T37" s="68"/>
-      <c r="U37" s="69"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="58"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="54"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="25" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="68"/>
-      <c r="O38" s="68"/>
-      <c r="P38" s="68"/>
-      <c r="Q38" s="68"/>
-      <c r="R38" s="68"/>
-      <c r="S38" s="68"/>
-      <c r="T38" s="68"/>
-      <c r="U38" s="69"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="58"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="50">
+      <c r="A39" s="62">
         <v>6</v>
       </c>
       <c r="B39" s="25" t="s">
@@ -3072,81 +3069,81 @@
       <c r="C39" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="68"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="68"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="68"/>
-      <c r="Q39" s="68"/>
-      <c r="R39" s="68"/>
-      <c r="S39" s="68"/>
-      <c r="T39" s="68"/>
-      <c r="U39" s="69"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="58"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="50"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="25" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="68"/>
-      <c r="S40" s="68"/>
-      <c r="T40" s="68"/>
-      <c r="U40" s="69"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
+      <c r="P40" s="57"/>
+      <c r="Q40" s="57"/>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="58"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="50"/>
+      <c r="A41" s="62"/>
       <c r="B41" s="25" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="70"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="71"/>
-      <c r="L41" s="71"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="71"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="71"/>
-      <c r="S41" s="71"/>
-      <c r="T41" s="71"/>
-      <c r="U41" s="72"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="61"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="50"/>
+      <c r="A42" s="62"/>
       <c r="B42" s="26" t="s">
         <v>82</v>
       </c>
@@ -3205,7 +3202,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="50"/>
+      <c r="A43" s="62"/>
       <c r="B43" s="26" t="s">
         <v>83</v>
       </c>
@@ -3234,7 +3231,7 @@
       <c r="U43" s="14"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="50"/>
+      <c r="A44" s="62"/>
       <c r="B44" s="28" t="s">
         <v>84</v>
       </c>
@@ -3261,7 +3258,7 @@
       <c r="U44" s="19"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="50"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="26" t="s">
         <v>85</v>
       </c>
@@ -3288,7 +3285,7 @@
       <c r="U45" s="14"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="54">
+      <c r="A46" s="52">
         <v>7</v>
       </c>
       <c r="B46" s="29" t="s">
@@ -3337,7 +3334,7 @@
       <c r="U46" s="5"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="54"/>
+      <c r="A47" s="52"/>
       <c r="B47" s="29" t="s">
         <v>87</v>
       </c>
@@ -3384,7 +3381,7 @@
       <c r="U47" s="5"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="54"/>
+      <c r="A48" s="52"/>
       <c r="B48" s="29" t="s">
         <v>88</v>
       </c>
@@ -3431,7 +3428,7 @@
       <c r="U48" s="5"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="54"/>
+      <c r="A49" s="52"/>
       <c r="B49" s="29" t="s">
         <v>89</v>
       </c>
@@ -3478,7 +3475,7 @@
       <c r="U49" s="5"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="54"/>
+      <c r="A50" s="52"/>
       <c r="B50" s="29" t="s">
         <v>90</v>
       </c>
@@ -3507,7 +3504,7 @@
       <c r="U50" s="5"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="54"/>
+      <c r="A51" s="52"/>
       <c r="B51" s="29" t="s">
         <v>91</v>
       </c>
@@ -3534,7 +3531,7 @@
       <c r="U51" s="5"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="54"/>
+      <c r="A52" s="52"/>
       <c r="B52" s="29" t="s">
         <v>92</v>
       </c>
@@ -3561,7 +3558,7 @@
       <c r="U52" s="5"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="50">
+      <c r="A53" s="62">
         <v>8</v>
       </c>
       <c r="B53" s="26" t="s">
@@ -3610,7 +3607,7 @@
       <c r="U53" s="14"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="50"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="26" t="s">
         <v>94</v>
       </c>
@@ -3626,7 +3623,7 @@
       <c r="F54" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="G54" s="79" t="s">
+      <c r="G54" s="50" t="s">
         <v>25</v>
       </c>
       <c r="H54" s="13" t="s">
@@ -3657,7 +3654,7 @@
       <c r="U54" s="14"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="50"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="26" t="s">
         <v>95</v>
       </c>
@@ -3704,7 +3701,7 @@
       <c r="U55" s="14"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="50"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="26" t="s">
         <v>96</v>
       </c>
@@ -3763,7 +3760,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="50"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="26" t="s">
         <v>97</v>
       </c>
@@ -3792,7 +3789,7 @@
       <c r="U57" s="14"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="50"/>
+      <c r="A58" s="62"/>
       <c r="B58" s="26" t="s">
         <v>98</v>
       </c>
@@ -3819,7 +3816,7 @@
       <c r="U58" s="14"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="50"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="26" t="s">
         <v>99</v>
       </c>
@@ -3846,7 +3843,7 @@
       <c r="U59" s="14"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="54">
+      <c r="A60" s="52">
         <v>9</v>
       </c>
       <c r="B60" s="29" t="s">
@@ -3895,7 +3892,7 @@
       <c r="U60" s="5"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="54"/>
+      <c r="A61" s="52"/>
       <c r="B61" s="29" t="s">
         <v>101</v>
       </c>
@@ -3942,7 +3939,7 @@
       <c r="U61" s="5"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="54"/>
+      <c r="A62" s="52"/>
       <c r="B62" s="29" t="s">
         <v>102</v>
       </c>
@@ -3989,7 +3986,7 @@
       <c r="U62" s="5"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="54"/>
+      <c r="A63" s="52"/>
       <c r="B63" s="29" t="s">
         <v>103</v>
       </c>
@@ -4048,7 +4045,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="54"/>
+      <c r="A64" s="52"/>
       <c r="B64" s="29" t="s">
         <v>104</v>
       </c>
@@ -4077,7 +4074,7 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="54"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="29" t="s">
         <v>105</v>
       </c>
@@ -4104,7 +4101,7 @@
       <c r="U65" s="6"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="54"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="29" t="s">
         <v>106</v>
       </c>
@@ -4131,7 +4128,7 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="50">
+      <c r="A67" s="62">
         <v>10</v>
       </c>
       <c r="B67" s="26" t="s">
@@ -4180,7 +4177,7 @@
       <c r="U67" s="15"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="50"/>
+      <c r="A68" s="62"/>
       <c r="B68" s="26" t="s">
         <v>108</v>
       </c>
@@ -4227,7 +4224,7 @@
       <c r="U68" s="15"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="50"/>
+      <c r="A69" s="62"/>
       <c r="B69" s="26" t="s">
         <v>109</v>
       </c>
@@ -4274,7 +4271,7 @@
       <c r="U69" s="15"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="50"/>
+      <c r="A70" s="62"/>
       <c r="B70" s="26" t="s">
         <v>110</v>
       </c>
@@ -4333,7 +4330,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="50"/>
+      <c r="A71" s="62"/>
       <c r="B71" s="26" t="s">
         <v>111</v>
       </c>
@@ -4362,7 +4359,7 @@
       <c r="U71" s="15"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="50"/>
+      <c r="A72" s="62"/>
       <c r="B72" s="26" t="s">
         <v>112</v>
       </c>
@@ -4389,7 +4386,7 @@
       <c r="U72" s="15"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="50"/>
+      <c r="A73" s="62"/>
       <c r="B73" s="26" t="s">
         <v>113</v>
       </c>
@@ -4416,7 +4413,7 @@
       <c r="U73" s="15"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="54">
+      <c r="A74" s="52">
         <v>11</v>
       </c>
       <c r="B74" s="29" t="s">
@@ -4465,7 +4462,7 @@
       <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="54"/>
+      <c r="A75" s="52"/>
       <c r="B75" s="29" t="s">
         <v>115</v>
       </c>
@@ -4512,7 +4509,7 @@
       <c r="U75" s="6"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="54"/>
+      <c r="A76" s="52"/>
       <c r="B76" s="29" t="s">
         <v>116</v>
       </c>
@@ -4559,7 +4556,7 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="54"/>
+      <c r="A77" s="52"/>
       <c r="B77" s="29" t="s">
         <v>117</v>
       </c>
@@ -4606,7 +4603,7 @@
       <c r="U77" s="5"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="54"/>
+      <c r="A78" s="52"/>
       <c r="B78" s="29" t="s">
         <v>118</v>
       </c>
@@ -4635,7 +4632,7 @@
       <c r="U78" s="5"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="54"/>
+      <c r="A79" s="52"/>
       <c r="B79" s="29" t="s">
         <v>119</v>
       </c>
@@ -4662,7 +4659,7 @@
       <c r="U79" s="5"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="54"/>
+      <c r="A80" s="52"/>
       <c r="B80" s="29" t="s">
         <v>120</v>
       </c>
@@ -4689,7 +4686,7 @@
       <c r="U80" s="5"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="50">
+      <c r="A81" s="62">
         <v>12</v>
       </c>
       <c r="B81" s="26" t="s">
@@ -4698,191 +4695,191 @@
       <c r="C81" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="55" t="s">
+      <c r="D81" s="71" t="s">
         <v>122</v>
       </c>
-      <c r="E81" s="56"/>
-      <c r="F81" s="56"/>
-      <c r="G81" s="56"/>
-      <c r="H81" s="56"/>
-      <c r="I81" s="56"/>
-      <c r="J81" s="56"/>
-      <c r="K81" s="56"/>
-      <c r="L81" s="56"/>
-      <c r="M81" s="56"/>
-      <c r="N81" s="56"/>
-      <c r="O81" s="56"/>
-      <c r="P81" s="56"/>
-      <c r="Q81" s="56"/>
-      <c r="R81" s="56"/>
-      <c r="S81" s="56"/>
-      <c r="T81" s="56"/>
-      <c r="U81" s="57"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="72"/>
+      <c r="H81" s="72"/>
+      <c r="I81" s="72"/>
+      <c r="J81" s="72"/>
+      <c r="K81" s="72"/>
+      <c r="L81" s="72"/>
+      <c r="M81" s="72"/>
+      <c r="N81" s="72"/>
+      <c r="O81" s="72"/>
+      <c r="P81" s="72"/>
+      <c r="Q81" s="72"/>
+      <c r="R81" s="72"/>
+      <c r="S81" s="72"/>
+      <c r="T81" s="72"/>
+      <c r="U81" s="73"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="50"/>
+      <c r="A82" s="62"/>
       <c r="B82" s="26" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="58"/>
-      <c r="E82" s="59"/>
-      <c r="F82" s="59"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="59"/>
-      <c r="J82" s="59"/>
-      <c r="K82" s="59"/>
-      <c r="L82" s="59"/>
-      <c r="M82" s="59"/>
-      <c r="N82" s="59"/>
-      <c r="O82" s="59"/>
-      <c r="P82" s="59"/>
-      <c r="Q82" s="59"/>
-      <c r="R82" s="59"/>
-      <c r="S82" s="59"/>
-      <c r="T82" s="59"/>
-      <c r="U82" s="60"/>
+      <c r="D82" s="74"/>
+      <c r="E82" s="75"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="75"/>
+      <c r="I82" s="75"/>
+      <c r="J82" s="75"/>
+      <c r="K82" s="75"/>
+      <c r="L82" s="75"/>
+      <c r="M82" s="75"/>
+      <c r="N82" s="75"/>
+      <c r="O82" s="75"/>
+      <c r="P82" s="75"/>
+      <c r="Q82" s="75"/>
+      <c r="R82" s="75"/>
+      <c r="S82" s="75"/>
+      <c r="T82" s="75"/>
+      <c r="U82" s="76"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="50"/>
+      <c r="A83" s="62"/>
       <c r="B83" s="26" t="s">
         <v>124</v>
       </c>
       <c r="C83" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D83" s="58"/>
-      <c r="E83" s="59"/>
-      <c r="F83" s="59"/>
-      <c r="G83" s="59"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="59"/>
-      <c r="J83" s="59"/>
-      <c r="K83" s="59"/>
-      <c r="L83" s="59"/>
-      <c r="M83" s="59"/>
-      <c r="N83" s="59"/>
-      <c r="O83" s="59"/>
-      <c r="P83" s="59"/>
-      <c r="Q83" s="59"/>
-      <c r="R83" s="59"/>
-      <c r="S83" s="59"/>
-      <c r="T83" s="59"/>
-      <c r="U83" s="60"/>
+      <c r="D83" s="74"/>
+      <c r="E83" s="75"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="75"/>
+      <c r="I83" s="75"/>
+      <c r="J83" s="75"/>
+      <c r="K83" s="75"/>
+      <c r="L83" s="75"/>
+      <c r="M83" s="75"/>
+      <c r="N83" s="75"/>
+      <c r="O83" s="75"/>
+      <c r="P83" s="75"/>
+      <c r="Q83" s="75"/>
+      <c r="R83" s="75"/>
+      <c r="S83" s="75"/>
+      <c r="T83" s="75"/>
+      <c r="U83" s="76"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="50"/>
+      <c r="A84" s="62"/>
       <c r="B84" s="26" t="s">
         <v>125</v>
       </c>
       <c r="C84" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D84" s="58"/>
-      <c r="E84" s="59"/>
-      <c r="F84" s="59"/>
-      <c r="G84" s="59"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="59"/>
-      <c r="J84" s="59"/>
-      <c r="K84" s="59"/>
-      <c r="L84" s="59"/>
-      <c r="M84" s="59"/>
-      <c r="N84" s="59"/>
-      <c r="O84" s="59"/>
-      <c r="P84" s="59"/>
-      <c r="Q84" s="59"/>
-      <c r="R84" s="59"/>
-      <c r="S84" s="59"/>
-      <c r="T84" s="59"/>
-      <c r="U84" s="60"/>
+      <c r="D84" s="74"/>
+      <c r="E84" s="75"/>
+      <c r="F84" s="75"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="75"/>
+      <c r="I84" s="75"/>
+      <c r="J84" s="75"/>
+      <c r="K84" s="75"/>
+      <c r="L84" s="75"/>
+      <c r="M84" s="75"/>
+      <c r="N84" s="75"/>
+      <c r="O84" s="75"/>
+      <c r="P84" s="75"/>
+      <c r="Q84" s="75"/>
+      <c r="R84" s="75"/>
+      <c r="S84" s="75"/>
+      <c r="T84" s="75"/>
+      <c r="U84" s="76"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="50"/>
+      <c r="A85" s="62"/>
       <c r="B85" s="26" t="s">
         <v>126</v>
       </c>
       <c r="C85" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="58"/>
-      <c r="E85" s="59"/>
-      <c r="F85" s="59"/>
-      <c r="G85" s="59"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="59"/>
-      <c r="J85" s="59"/>
-      <c r="K85" s="59"/>
-      <c r="L85" s="59"/>
-      <c r="M85" s="59"/>
-      <c r="N85" s="59"/>
-      <c r="O85" s="59"/>
-      <c r="P85" s="59"/>
-      <c r="Q85" s="59"/>
-      <c r="R85" s="59"/>
-      <c r="S85" s="59"/>
-      <c r="T85" s="59"/>
-      <c r="U85" s="60"/>
+      <c r="D85" s="74"/>
+      <c r="E85" s="75"/>
+      <c r="F85" s="75"/>
+      <c r="G85" s="75"/>
+      <c r="H85" s="75"/>
+      <c r="I85" s="75"/>
+      <c r="J85" s="75"/>
+      <c r="K85" s="75"/>
+      <c r="L85" s="75"/>
+      <c r="M85" s="75"/>
+      <c r="N85" s="75"/>
+      <c r="O85" s="75"/>
+      <c r="P85" s="75"/>
+      <c r="Q85" s="75"/>
+      <c r="R85" s="75"/>
+      <c r="S85" s="75"/>
+      <c r="T85" s="75"/>
+      <c r="U85" s="76"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="50"/>
+      <c r="A86" s="62"/>
       <c r="B86" s="26" t="s">
         <v>127</v>
       </c>
       <c r="C86" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D86" s="58"/>
-      <c r="E86" s="59"/>
-      <c r="F86" s="59"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="59"/>
-      <c r="J86" s="59"/>
-      <c r="K86" s="59"/>
-      <c r="L86" s="59"/>
-      <c r="M86" s="59"/>
-      <c r="N86" s="59"/>
-      <c r="O86" s="59"/>
-      <c r="P86" s="59"/>
-      <c r="Q86" s="59"/>
-      <c r="R86" s="59"/>
-      <c r="S86" s="59"/>
-      <c r="T86" s="59"/>
-      <c r="U86" s="60"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="75"/>
+      <c r="F86" s="75"/>
+      <c r="G86" s="75"/>
+      <c r="H86" s="75"/>
+      <c r="I86" s="75"/>
+      <c r="J86" s="75"/>
+      <c r="K86" s="75"/>
+      <c r="L86" s="75"/>
+      <c r="M86" s="75"/>
+      <c r="N86" s="75"/>
+      <c r="O86" s="75"/>
+      <c r="P86" s="75"/>
+      <c r="Q86" s="75"/>
+      <c r="R86" s="75"/>
+      <c r="S86" s="75"/>
+      <c r="T86" s="75"/>
+      <c r="U86" s="76"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="50"/>
+      <c r="A87" s="62"/>
       <c r="B87" s="26" t="s">
         <v>128</v>
       </c>
       <c r="C87" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D87" s="58"/>
-      <c r="E87" s="59"/>
-      <c r="F87" s="59"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="59"/>
-      <c r="J87" s="59"/>
-      <c r="K87" s="59"/>
-      <c r="L87" s="59"/>
-      <c r="M87" s="59"/>
-      <c r="N87" s="59"/>
-      <c r="O87" s="59"/>
-      <c r="P87" s="59"/>
-      <c r="Q87" s="59"/>
-      <c r="R87" s="59"/>
-      <c r="S87" s="59"/>
-      <c r="T87" s="59"/>
-      <c r="U87" s="60"/>
+      <c r="D87" s="74"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="75"/>
+      <c r="G87" s="75"/>
+      <c r="H87" s="75"/>
+      <c r="I87" s="75"/>
+      <c r="J87" s="75"/>
+      <c r="K87" s="75"/>
+      <c r="L87" s="75"/>
+      <c r="M87" s="75"/>
+      <c r="N87" s="75"/>
+      <c r="O87" s="75"/>
+      <c r="P87" s="75"/>
+      <c r="Q87" s="75"/>
+      <c r="R87" s="75"/>
+      <c r="S87" s="75"/>
+      <c r="T87" s="75"/>
+      <c r="U87" s="76"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="54">
+      <c r="A88" s="52">
         <v>13</v>
       </c>
       <c r="B88" s="29" t="s">
@@ -4891,189 +4888,189 @@
       <c r="C88" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="58"/>
-      <c r="E88" s="59"/>
-      <c r="F88" s="59"/>
-      <c r="G88" s="59"/>
-      <c r="H88" s="59"/>
-      <c r="I88" s="59"/>
-      <c r="J88" s="59"/>
-      <c r="K88" s="59"/>
-      <c r="L88" s="59"/>
-      <c r="M88" s="59"/>
-      <c r="N88" s="59"/>
-      <c r="O88" s="59"/>
-      <c r="P88" s="59"/>
-      <c r="Q88" s="59"/>
-      <c r="R88" s="59"/>
-      <c r="S88" s="59"/>
-      <c r="T88" s="59"/>
-      <c r="U88" s="60"/>
+      <c r="D88" s="74"/>
+      <c r="E88" s="75"/>
+      <c r="F88" s="75"/>
+      <c r="G88" s="75"/>
+      <c r="H88" s="75"/>
+      <c r="I88" s="75"/>
+      <c r="J88" s="75"/>
+      <c r="K88" s="75"/>
+      <c r="L88" s="75"/>
+      <c r="M88" s="75"/>
+      <c r="N88" s="75"/>
+      <c r="O88" s="75"/>
+      <c r="P88" s="75"/>
+      <c r="Q88" s="75"/>
+      <c r="R88" s="75"/>
+      <c r="S88" s="75"/>
+      <c r="T88" s="75"/>
+      <c r="U88" s="76"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="54"/>
+      <c r="A89" s="52"/>
       <c r="B89" s="29" t="s">
         <v>130</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="58"/>
-      <c r="E89" s="59"/>
-      <c r="F89" s="59"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="59"/>
-      <c r="I89" s="59"/>
-      <c r="J89" s="59"/>
-      <c r="K89" s="59"/>
-      <c r="L89" s="59"/>
-      <c r="M89" s="59"/>
-      <c r="N89" s="59"/>
-      <c r="O89" s="59"/>
-      <c r="P89" s="59"/>
-      <c r="Q89" s="59"/>
-      <c r="R89" s="59"/>
-      <c r="S89" s="59"/>
-      <c r="T89" s="59"/>
-      <c r="U89" s="60"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="75"/>
+      <c r="F89" s="75"/>
+      <c r="G89" s="75"/>
+      <c r="H89" s="75"/>
+      <c r="I89" s="75"/>
+      <c r="J89" s="75"/>
+      <c r="K89" s="75"/>
+      <c r="L89" s="75"/>
+      <c r="M89" s="75"/>
+      <c r="N89" s="75"/>
+      <c r="O89" s="75"/>
+      <c r="P89" s="75"/>
+      <c r="Q89" s="75"/>
+      <c r="R89" s="75"/>
+      <c r="S89" s="75"/>
+      <c r="T89" s="75"/>
+      <c r="U89" s="76"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="54"/>
+      <c r="A90" s="52"/>
       <c r="B90" s="29" t="s">
         <v>131</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D90" s="58"/>
-      <c r="E90" s="59"/>
-      <c r="F90" s="59"/>
-      <c r="G90" s="59"/>
-      <c r="H90" s="59"/>
-      <c r="I90" s="59"/>
-      <c r="J90" s="59"/>
-      <c r="K90" s="59"/>
-      <c r="L90" s="59"/>
-      <c r="M90" s="59"/>
-      <c r="N90" s="59"/>
-      <c r="O90" s="59"/>
-      <c r="P90" s="59"/>
-      <c r="Q90" s="59"/>
-      <c r="R90" s="59"/>
-      <c r="S90" s="59"/>
-      <c r="T90" s="59"/>
-      <c r="U90" s="60"/>
+      <c r="D90" s="74"/>
+      <c r="E90" s="75"/>
+      <c r="F90" s="75"/>
+      <c r="G90" s="75"/>
+      <c r="H90" s="75"/>
+      <c r="I90" s="75"/>
+      <c r="J90" s="75"/>
+      <c r="K90" s="75"/>
+      <c r="L90" s="75"/>
+      <c r="M90" s="75"/>
+      <c r="N90" s="75"/>
+      <c r="O90" s="75"/>
+      <c r="P90" s="75"/>
+      <c r="Q90" s="75"/>
+      <c r="R90" s="75"/>
+      <c r="S90" s="75"/>
+      <c r="T90" s="75"/>
+      <c r="U90" s="76"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="54"/>
+      <c r="A91" s="52"/>
       <c r="B91" s="29" t="s">
         <v>132</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D91" s="58"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="59"/>
-      <c r="G91" s="59"/>
-      <c r="H91" s="59"/>
-      <c r="I91" s="59"/>
-      <c r="J91" s="59"/>
-      <c r="K91" s="59"/>
-      <c r="L91" s="59"/>
-      <c r="M91" s="59"/>
-      <c r="N91" s="59"/>
-      <c r="O91" s="59"/>
-      <c r="P91" s="59"/>
-      <c r="Q91" s="59"/>
-      <c r="R91" s="59"/>
-      <c r="S91" s="59"/>
-      <c r="T91" s="59"/>
-      <c r="U91" s="60"/>
+      <c r="D91" s="74"/>
+      <c r="E91" s="75"/>
+      <c r="F91" s="75"/>
+      <c r="G91" s="75"/>
+      <c r="H91" s="75"/>
+      <c r="I91" s="75"/>
+      <c r="J91" s="75"/>
+      <c r="K91" s="75"/>
+      <c r="L91" s="75"/>
+      <c r="M91" s="75"/>
+      <c r="N91" s="75"/>
+      <c r="O91" s="75"/>
+      <c r="P91" s="75"/>
+      <c r="Q91" s="75"/>
+      <c r="R91" s="75"/>
+      <c r="S91" s="75"/>
+      <c r="T91" s="75"/>
+      <c r="U91" s="76"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="54"/>
+      <c r="A92" s="52"/>
       <c r="B92" s="29" t="s">
         <v>133</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D92" s="58"/>
-      <c r="E92" s="59"/>
-      <c r="F92" s="59"/>
-      <c r="G92" s="59"/>
-      <c r="H92" s="59"/>
-      <c r="I92" s="59"/>
-      <c r="J92" s="59"/>
-      <c r="K92" s="59"/>
-      <c r="L92" s="59"/>
-      <c r="M92" s="59"/>
-      <c r="N92" s="59"/>
-      <c r="O92" s="59"/>
-      <c r="P92" s="59"/>
-      <c r="Q92" s="59"/>
-      <c r="R92" s="59"/>
-      <c r="S92" s="59"/>
-      <c r="T92" s="59"/>
-      <c r="U92" s="60"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="75"/>
+      <c r="F92" s="75"/>
+      <c r="G92" s="75"/>
+      <c r="H92" s="75"/>
+      <c r="I92" s="75"/>
+      <c r="J92" s="75"/>
+      <c r="K92" s="75"/>
+      <c r="L92" s="75"/>
+      <c r="M92" s="75"/>
+      <c r="N92" s="75"/>
+      <c r="O92" s="75"/>
+      <c r="P92" s="75"/>
+      <c r="Q92" s="75"/>
+      <c r="R92" s="75"/>
+      <c r="S92" s="75"/>
+      <c r="T92" s="75"/>
+      <c r="U92" s="76"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="54"/>
+      <c r="A93" s="52"/>
       <c r="B93" s="29" t="s">
         <v>134</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D93" s="58"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="59"/>
-      <c r="J93" s="59"/>
-      <c r="K93" s="59"/>
-      <c r="L93" s="59"/>
-      <c r="M93" s="59"/>
-      <c r="N93" s="59"/>
-      <c r="O93" s="59"/>
-      <c r="P93" s="59"/>
-      <c r="Q93" s="59"/>
-      <c r="R93" s="59"/>
-      <c r="S93" s="59"/>
-      <c r="T93" s="59"/>
-      <c r="U93" s="60"/>
+      <c r="D93" s="74"/>
+      <c r="E93" s="75"/>
+      <c r="F93" s="75"/>
+      <c r="G93" s="75"/>
+      <c r="H93" s="75"/>
+      <c r="I93" s="75"/>
+      <c r="J93" s="75"/>
+      <c r="K93" s="75"/>
+      <c r="L93" s="75"/>
+      <c r="M93" s="75"/>
+      <c r="N93" s="75"/>
+      <c r="O93" s="75"/>
+      <c r="P93" s="75"/>
+      <c r="Q93" s="75"/>
+      <c r="R93" s="75"/>
+      <c r="S93" s="75"/>
+      <c r="T93" s="75"/>
+      <c r="U93" s="76"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="54"/>
+      <c r="A94" s="52"/>
       <c r="B94" s="29" t="s">
         <v>135</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D94" s="61"/>
-      <c r="E94" s="62"/>
-      <c r="F94" s="62"/>
-      <c r="G94" s="62"/>
-      <c r="H94" s="62"/>
-      <c r="I94" s="62"/>
-      <c r="J94" s="62"/>
-      <c r="K94" s="62"/>
-      <c r="L94" s="62"/>
-      <c r="M94" s="62"/>
-      <c r="N94" s="62"/>
-      <c r="O94" s="62"/>
-      <c r="P94" s="62"/>
-      <c r="Q94" s="62"/>
-      <c r="R94" s="62"/>
-      <c r="S94" s="62"/>
-      <c r="T94" s="62"/>
-      <c r="U94" s="63"/>
+      <c r="D94" s="77"/>
+      <c r="E94" s="78"/>
+      <c r="F94" s="78"/>
+      <c r="G94" s="78"/>
+      <c r="H94" s="78"/>
+      <c r="I94" s="78"/>
+      <c r="J94" s="78"/>
+      <c r="K94" s="78"/>
+      <c r="L94" s="78"/>
+      <c r="M94" s="78"/>
+      <c r="N94" s="78"/>
+      <c r="O94" s="78"/>
+      <c r="P94" s="78"/>
+      <c r="Q94" s="78"/>
+      <c r="R94" s="78"/>
+      <c r="S94" s="78"/>
+      <c r="T94" s="78"/>
+      <c r="U94" s="79"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="50">
+      <c r="A95" s="62">
         <v>14</v>
       </c>
       <c r="B95" s="26" t="s">
@@ -5106,7 +5103,7 @@
       <c r="U95" s="14"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="50"/>
+      <c r="A96" s="62"/>
       <c r="B96" s="26" t="s">
         <v>138</v>
       </c>
@@ -5137,7 +5134,7 @@
       <c r="U96" s="14"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="50"/>
+      <c r="A97" s="62"/>
       <c r="B97" s="26" t="s">
         <v>139</v>
       </c>
@@ -5168,7 +5165,7 @@
       <c r="U97" s="14"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="50"/>
+      <c r="A98" s="62"/>
       <c r="B98" s="26" t="s">
         <v>140</v>
       </c>
@@ -5199,7 +5196,7 @@
       <c r="U98" s="14"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="50"/>
+      <c r="A99" s="62"/>
       <c r="B99" s="26" t="s">
         <v>141</v>
       </c>
@@ -5230,7 +5227,7 @@
       <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="50"/>
+      <c r="A100" s="62"/>
       <c r="B100" s="26" t="s">
         <v>142</v>
       </c>
@@ -5261,7 +5258,7 @@
       <c r="U100" s="14"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="50"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="26" t="s">
         <v>143</v>
       </c>
@@ -5292,7 +5289,7 @@
       <c r="U101" s="14"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="54">
+      <c r="A102" s="52">
         <v>15</v>
       </c>
       <c r="B102" s="29" t="s">
@@ -5325,7 +5322,7 @@
       <c r="U102" s="5"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="54"/>
+      <c r="A103" s="52"/>
       <c r="B103" s="29" t="s">
         <v>145</v>
       </c>
@@ -5356,7 +5353,7 @@
       <c r="U103" s="5"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="54"/>
+      <c r="A104" s="52"/>
       <c r="B104" s="29" t="s">
         <v>146</v>
       </c>
@@ -5387,7 +5384,7 @@
       <c r="U104" s="5"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="54"/>
+      <c r="A105" s="52"/>
       <c r="B105" s="29" t="s">
         <v>147</v>
       </c>
@@ -5418,7 +5415,7 @@
       <c r="U105" s="5"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="54"/>
+      <c r="A106" s="52"/>
       <c r="B106" s="29" t="s">
         <v>148</v>
       </c>
@@ -5449,7 +5446,7 @@
       <c r="U106" s="5"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="54"/>
+      <c r="A107" s="52"/>
       <c r="B107" s="29" t="s">
         <v>149</v>
       </c>
@@ -5480,7 +5477,7 @@
       <c r="U107" s="5"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="54"/>
+      <c r="A108" s="52"/>
       <c r="B108" s="29" t="s">
         <v>150</v>
       </c>
@@ -5511,7 +5508,7 @@
       <c r="U108" s="5"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="50">
+      <c r="A109" s="62">
         <v>16</v>
       </c>
       <c r="B109" s="26" t="s">
@@ -5544,7 +5541,7 @@
       <c r="U109" s="15"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="50"/>
+      <c r="A110" s="62"/>
       <c r="B110" s="26" t="s">
         <v>152</v>
       </c>
@@ -5575,7 +5572,7 @@
       <c r="U110" s="15"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="50"/>
+      <c r="A111" s="62"/>
       <c r="B111" s="26" t="s">
         <v>153</v>
       </c>
@@ -5606,7 +5603,7 @@
       <c r="U111" s="15"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="50"/>
+      <c r="A112" s="62"/>
       <c r="B112" s="26" t="s">
         <v>154</v>
       </c>
@@ -5637,7 +5634,7 @@
       <c r="U112" s="15"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="50"/>
+      <c r="A113" s="62"/>
       <c r="B113" s="26" t="s">
         <v>155</v>
       </c>
@@ -5668,7 +5665,7 @@
       <c r="U113" s="15"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="50"/>
+      <c r="A114" s="62"/>
       <c r="B114" s="26" t="s">
         <v>156</v>
       </c>
@@ -5699,7 +5696,7 @@
       <c r="U114" s="15"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="50"/>
+      <c r="A115" s="62"/>
       <c r="B115" s="26" t="s">
         <v>157</v>
       </c>
@@ -5730,7 +5727,7 @@
       <c r="U115" s="15"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="54">
+      <c r="A116" s="52">
         <v>17</v>
       </c>
       <c r="B116" s="29" t="s">
@@ -5763,7 +5760,7 @@
       <c r="U116" s="5"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="54"/>
+      <c r="A117" s="52"/>
       <c r="B117" s="29" t="s">
         <v>159</v>
       </c>
@@ -5794,7 +5791,7 @@
       <c r="U117" s="5"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="54"/>
+      <c r="A118" s="52"/>
       <c r="B118" s="29" t="s">
         <v>160</v>
       </c>
@@ -5825,7 +5822,7 @@
       <c r="U118" s="5"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="54"/>
+      <c r="A119" s="52"/>
       <c r="B119" s="29" t="s">
         <v>161</v>
       </c>
@@ -5856,7 +5853,7 @@
       <c r="U119" s="5"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="54"/>
+      <c r="A120" s="52"/>
       <c r="B120" s="29" t="s">
         <v>162</v>
       </c>
@@ -5887,7 +5884,7 @@
       <c r="U120" s="5"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="54"/>
+      <c r="A121" s="52"/>
       <c r="B121" s="29" t="s">
         <v>163</v>
       </c>
@@ -5918,7 +5915,7 @@
       <c r="U121" s="5"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="54"/>
+      <c r="A122" s="52"/>
       <c r="B122" s="29" t="s">
         <v>164</v>
       </c>
@@ -5949,7 +5946,7 @@
       <c r="U122" s="5"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="50">
+      <c r="A123" s="62">
         <v>18</v>
       </c>
       <c r="B123" s="26" t="s">
@@ -5982,7 +5979,7 @@
       <c r="U123" s="15"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="50"/>
+      <c r="A124" s="62"/>
       <c r="B124" s="26" t="s">
         <v>166</v>
       </c>
@@ -6013,7 +6010,7 @@
       <c r="U124" s="15"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="50"/>
+      <c r="A125" s="62"/>
       <c r="B125" s="26" t="s">
         <v>167</v>
       </c>
@@ -6044,7 +6041,7 @@
       <c r="U125" s="15"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="50"/>
+      <c r="A126" s="62"/>
       <c r="B126" s="26" t="s">
         <v>168</v>
       </c>
@@ -6075,36 +6072,36 @@
       <c r="U126" s="15"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="50"/>
+      <c r="A127" s="62"/>
       <c r="B127" s="25" t="s">
         <v>169</v>
       </c>
       <c r="C127" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="D127" s="51" t="s">
+      <c r="D127" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="E127" s="52"/>
-      <c r="F127" s="52"/>
-      <c r="G127" s="52"/>
-      <c r="H127" s="52"/>
-      <c r="I127" s="52"/>
-      <c r="J127" s="52"/>
-      <c r="K127" s="52"/>
-      <c r="L127" s="52"/>
-      <c r="M127" s="52"/>
-      <c r="N127" s="52"/>
-      <c r="O127" s="52"/>
-      <c r="P127" s="52"/>
-      <c r="Q127" s="52"/>
-      <c r="R127" s="52"/>
-      <c r="S127" s="52"/>
-      <c r="T127" s="52"/>
-      <c r="U127" s="53"/>
+      <c r="E127" s="69"/>
+      <c r="F127" s="69"/>
+      <c r="G127" s="69"/>
+      <c r="H127" s="69"/>
+      <c r="I127" s="69"/>
+      <c r="J127" s="69"/>
+      <c r="K127" s="69"/>
+      <c r="L127" s="69"/>
+      <c r="M127" s="69"/>
+      <c r="N127" s="69"/>
+      <c r="O127" s="69"/>
+      <c r="P127" s="69"/>
+      <c r="Q127" s="69"/>
+      <c r="R127" s="69"/>
+      <c r="S127" s="69"/>
+      <c r="T127" s="69"/>
+      <c r="U127" s="70"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="50"/>
+      <c r="A128" s="62"/>
       <c r="B128" s="26" t="s">
         <v>171</v>
       </c>
@@ -6135,7 +6132,7 @@
       <c r="U128" s="15"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="50"/>
+      <c r="A129" s="62"/>
       <c r="B129" s="26" t="s">
         <v>172</v>
       </c>
@@ -6166,7 +6163,7 @@
       <c r="U129" s="15"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="54">
+      <c r="A130" s="52">
         <v>19</v>
       </c>
       <c r="B130" s="29" t="s">
@@ -6199,7 +6196,7 @@
       <c r="U130" s="5"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="54"/>
+      <c r="A131" s="52"/>
       <c r="B131" s="29" t="s">
         <v>174</v>
       </c>
@@ -6230,7 +6227,7 @@
       <c r="U131" s="5"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="54"/>
+      <c r="A132" s="52"/>
       <c r="B132" s="29" t="s">
         <v>175</v>
       </c>
@@ -6261,7 +6258,7 @@
       <c r="U132" s="5"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="54"/>
+      <c r="A133" s="52"/>
       <c r="B133" s="29" t="s">
         <v>176</v>
       </c>
@@ -6292,7 +6289,7 @@
       <c r="U133" s="5"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="54"/>
+      <c r="A134" s="52"/>
       <c r="B134" s="29" t="s">
         <v>177</v>
       </c>
@@ -6323,7 +6320,7 @@
       <c r="U134" s="5"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="54"/>
+      <c r="A135" s="52"/>
       <c r="B135" s="29" t="s">
         <v>178</v>
       </c>
@@ -6354,7 +6351,7 @@
       <c r="U135" s="5"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="54"/>
+      <c r="A136" s="52"/>
       <c r="B136" s="29" t="s">
         <v>179</v>
       </c>
@@ -6400,6 +6397,27 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="D29:U31"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
@@ -6416,27 +6434,6 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6479,81 +6476,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="65"/>
+      <c r="D2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73" t="s">
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73" t="s">
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73" t="s">
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73" t="s">
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="73"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="74" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="73" t="s">
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73" t="s">
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73" t="s">
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73" t="s">
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="54">
+      <c r="A4" s="52">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -6611,7 +6608,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="54"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -6675,7 +6672,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="54"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
@@ -6739,7 +6736,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="54"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
@@ -6801,7 +6798,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="54"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
@@ -6847,7 +6844,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="54"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
@@ -6889,7 +6886,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="54"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
@@ -6933,7 +6930,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="50">
+      <c r="A11" s="62">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -6997,7 +6994,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="50"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="11" t="s">
         <v>48</v>
       </c>
@@ -7059,7 +7056,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="50"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="11" t="s">
         <v>49</v>
       </c>
@@ -7111,7 +7108,7 @@
       <c r="AA13" s="10"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="50"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="11" t="s">
         <v>50</v>
       </c>
@@ -7175,7 +7172,7 @@
       <c r="AA14" s="10"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="50"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="11" t="s">
         <v>54</v>
       </c>
@@ -7204,7 +7201,7 @@
       <c r="U15" s="14"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="50"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="11" t="s">
         <v>55</v>
       </c>
@@ -7231,7 +7228,7 @@
       <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="50"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="11" t="s">
         <v>56</v>
       </c>
@@ -7258,7 +7255,7 @@
       <c r="U17" s="14"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="54">
+      <c r="A18" s="52">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -7307,7 +7304,7 @@
       <c r="U18" s="5"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="54"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
@@ -7354,7 +7351,7 @@
       <c r="U19" s="5"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="54"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
@@ -7401,7 +7398,7 @@
       <c r="U20" s="5"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="54"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
@@ -7460,7 +7457,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="54"/>
+      <c r="A22" s="52"/>
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -7489,7 +7486,7 @@
       <c r="U22" s="5"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="54"/>
+      <c r="A23" s="52"/>
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -7516,7 +7513,7 @@
       <c r="U23" s="5"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="54"/>
+      <c r="A24" s="52"/>
       <c r="B24" s="16" t="s">
         <v>63</v>
       </c>
@@ -7543,7 +7540,7 @@
       <c r="U24" s="19"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="50">
+      <c r="A25" s="62">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -7592,7 +7589,7 @@
       <c r="U25" s="14"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="50"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="11" t="s">
         <v>65</v>
       </c>
@@ -7639,7 +7636,7 @@
       <c r="U26" s="14"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="50"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="11" t="s">
         <v>66</v>
       </c>
@@ -7686,7 +7683,7 @@
       <c r="U27" s="14"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="50"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="11" t="s">
         <v>67</v>
       </c>
@@ -7733,90 +7730,90 @@
       <c r="U28" s="14"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="50"/>
+      <c r="A29" s="62"/>
       <c r="B29" s="23" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="64" t="s">
+      <c r="D29" s="53" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="66"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="55"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="50"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="23" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="67"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
-      <c r="M30" s="68"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="68"/>
-      <c r="P30" s="68"/>
-      <c r="Q30" s="68"/>
-      <c r="R30" s="68"/>
-      <c r="S30" s="68"/>
-      <c r="T30" s="68"/>
-      <c r="U30" s="69"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="58"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="50"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="23" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="70"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="72"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="54">
+      <c r="A32" s="52">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -7865,7 +7862,7 @@
       <c r="U32" s="5"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="54"/>
+      <c r="A33" s="52"/>
       <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
@@ -7912,7 +7909,7 @@
       <c r="U33" s="5"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="54"/>
+      <c r="A34" s="52"/>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
@@ -7959,117 +7956,117 @@
       <c r="U34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="54"/>
+      <c r="A35" s="52"/>
       <c r="B35" s="46" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="64" t="s">
+      <c r="D35" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="65"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="66"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="54"/>
+      <c r="A36" s="52"/>
       <c r="B36" s="46" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="68"/>
-      <c r="M36" s="68"/>
-      <c r="N36" s="68"/>
-      <c r="O36" s="68"/>
-      <c r="P36" s="68"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="68"/>
-      <c r="T36" s="68"/>
-      <c r="U36" s="69"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="57"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="58"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="54"/>
+      <c r="A37" s="52"/>
       <c r="B37" s="46" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
-      <c r="L37" s="68"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="68"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="68"/>
-      <c r="Q37" s="68"/>
-      <c r="R37" s="68"/>
-      <c r="S37" s="68"/>
-      <c r="T37" s="68"/>
-      <c r="U37" s="69"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="58"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="54"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="46" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="68"/>
-      <c r="O38" s="68"/>
-      <c r="P38" s="68"/>
-      <c r="Q38" s="68"/>
-      <c r="R38" s="68"/>
-      <c r="S38" s="68"/>
-      <c r="T38" s="68"/>
-      <c r="U38" s="69"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="58"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="50">
+      <c r="A39" s="62">
         <v>6</v>
       </c>
       <c r="B39" s="46" t="s">
@@ -8078,81 +8075,81 @@
       <c r="C39" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="68"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="68"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="68"/>
-      <c r="Q39" s="68"/>
-      <c r="R39" s="68"/>
-      <c r="S39" s="68"/>
-      <c r="T39" s="68"/>
-      <c r="U39" s="69"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="58"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="50"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="46" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="68"/>
-      <c r="S40" s="68"/>
-      <c r="T40" s="68"/>
-      <c r="U40" s="69"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
+      <c r="P40" s="57"/>
+      <c r="Q40" s="57"/>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="58"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="50"/>
+      <c r="A41" s="62"/>
       <c r="B41" s="46" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="70"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="71"/>
-      <c r="L41" s="71"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="71"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="71"/>
-      <c r="S41" s="71"/>
-      <c r="T41" s="71"/>
-      <c r="U41" s="72"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="61"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="50"/>
+      <c r="A42" s="62"/>
       <c r="B42" s="47" t="s">
         <v>82</v>
       </c>
@@ -8211,7 +8208,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="50"/>
+      <c r="A43" s="62"/>
       <c r="B43" s="47" t="s">
         <v>83</v>
       </c>
@@ -8240,7 +8237,7 @@
       <c r="U43" s="14"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="50"/>
+      <c r="A44" s="62"/>
       <c r="B44" s="48" t="s">
         <v>84</v>
       </c>
@@ -8267,7 +8264,7 @@
       <c r="U44" s="19"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="50"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="47" t="s">
         <v>85</v>
       </c>
@@ -8294,7 +8291,7 @@
       <c r="U45" s="14"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="54">
+      <c r="A46" s="52">
         <v>7</v>
       </c>
       <c r="B46" s="49" t="s">
@@ -8343,7 +8340,7 @@
       <c r="U46" s="5"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="54"/>
+      <c r="A47" s="52"/>
       <c r="B47" s="49" t="s">
         <v>87</v>
       </c>
@@ -8390,7 +8387,7 @@
       <c r="U47" s="5"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="54"/>
+      <c r="A48" s="52"/>
       <c r="B48" s="49" t="s">
         <v>88</v>
       </c>
@@ -8437,7 +8434,7 @@
       <c r="U48" s="5"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="54"/>
+      <c r="A49" s="52"/>
       <c r="B49" s="49" t="s">
         <v>89</v>
       </c>
@@ -8484,7 +8481,7 @@
       <c r="U49" s="5"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="54"/>
+      <c r="A50" s="52"/>
       <c r="B50" s="49" t="s">
         <v>90</v>
       </c>
@@ -8513,7 +8510,7 @@
       <c r="U50" s="5"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="54"/>
+      <c r="A51" s="52"/>
       <c r="B51" s="49" t="s">
         <v>91</v>
       </c>
@@ -8540,7 +8537,7 @@
       <c r="U51" s="5"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="54"/>
+      <c r="A52" s="52"/>
       <c r="B52" s="49" t="s">
         <v>92</v>
       </c>
@@ -8567,7 +8564,7 @@
       <c r="U52" s="5"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="50">
+      <c r="A53" s="62">
         <v>8</v>
       </c>
       <c r="B53" s="47" t="s">
@@ -8616,7 +8613,7 @@
       <c r="U53" s="14"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="50"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="47" t="s">
         <v>94</v>
       </c>
@@ -8663,7 +8660,7 @@
       <c r="U54" s="14"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="50"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="47" t="s">
         <v>95</v>
       </c>
@@ -8710,7 +8707,7 @@
       <c r="U55" s="14"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="50"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="47" t="s">
         <v>96</v>
       </c>
@@ -8769,7 +8766,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="50"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="47" t="s">
         <v>97</v>
       </c>
@@ -8798,7 +8795,7 @@
       <c r="U57" s="14"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="50"/>
+      <c r="A58" s="62"/>
       <c r="B58" s="47" t="s">
         <v>98</v>
       </c>
@@ -8825,7 +8822,7 @@
       <c r="U58" s="14"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="50"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="47" t="s">
         <v>99</v>
       </c>
@@ -8852,7 +8849,7 @@
       <c r="U59" s="14"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="54">
+      <c r="A60" s="52">
         <v>9</v>
       </c>
       <c r="B60" s="49" t="s">
@@ -8901,7 +8898,7 @@
       <c r="U60" s="5"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="54"/>
+      <c r="A61" s="52"/>
       <c r="B61" s="49" t="s">
         <v>101</v>
       </c>
@@ -8948,7 +8945,7 @@
       <c r="U61" s="5"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="54"/>
+      <c r="A62" s="52"/>
       <c r="B62" s="49" t="s">
         <v>102</v>
       </c>
@@ -8995,7 +8992,7 @@
       <c r="U62" s="5"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="54"/>
+      <c r="A63" s="52"/>
       <c r="B63" s="49" t="s">
         <v>103</v>
       </c>
@@ -9054,7 +9051,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="54"/>
+      <c r="A64" s="52"/>
       <c r="B64" s="49" t="s">
         <v>104</v>
       </c>
@@ -9083,7 +9080,7 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="54"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="49" t="s">
         <v>105</v>
       </c>
@@ -9110,7 +9107,7 @@
       <c r="U65" s="6"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="54"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="49" t="s">
         <v>106</v>
       </c>
@@ -9137,7 +9134,7 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="50">
+      <c r="A67" s="62">
         <v>10</v>
       </c>
       <c r="B67" s="47" t="s">
@@ -9186,7 +9183,7 @@
       <c r="U67" s="15"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="50"/>
+      <c r="A68" s="62"/>
       <c r="B68" s="47" t="s">
         <v>108</v>
       </c>
@@ -9233,7 +9230,7 @@
       <c r="U68" s="15"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="50"/>
+      <c r="A69" s="62"/>
       <c r="B69" s="47" t="s">
         <v>109</v>
       </c>
@@ -9280,7 +9277,7 @@
       <c r="U69" s="15"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="50"/>
+      <c r="A70" s="62"/>
       <c r="B70" s="47" t="s">
         <v>110</v>
       </c>
@@ -9339,7 +9336,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="50"/>
+      <c r="A71" s="62"/>
       <c r="B71" s="47" t="s">
         <v>111</v>
       </c>
@@ -9368,7 +9365,7 @@
       <c r="U71" s="15"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="50"/>
+      <c r="A72" s="62"/>
       <c r="B72" s="47" t="s">
         <v>112</v>
       </c>
@@ -9395,7 +9392,7 @@
       <c r="U72" s="15"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="50"/>
+      <c r="A73" s="62"/>
       <c r="B73" s="47" t="s">
         <v>113</v>
       </c>
@@ -9422,7 +9419,7 @@
       <c r="U73" s="15"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="54">
+      <c r="A74" s="52">
         <v>11</v>
       </c>
       <c r="B74" s="49" t="s">
@@ -9471,7 +9468,7 @@
       <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="54"/>
+      <c r="A75" s="52"/>
       <c r="B75" s="49" t="s">
         <v>115</v>
       </c>
@@ -9518,7 +9515,7 @@
       <c r="U75" s="6"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="54"/>
+      <c r="A76" s="52"/>
       <c r="B76" s="49" t="s">
         <v>116</v>
       </c>
@@ -9565,7 +9562,7 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="54"/>
+      <c r="A77" s="52"/>
       <c r="B77" s="49" t="s">
         <v>117</v>
       </c>
@@ -9612,7 +9609,7 @@
       <c r="U77" s="5"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="54"/>
+      <c r="A78" s="52"/>
       <c r="B78" s="49" t="s">
         <v>118</v>
       </c>
@@ -9641,7 +9638,7 @@
       <c r="U78" s="5"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="54"/>
+      <c r="A79" s="52"/>
       <c r="B79" s="49" t="s">
         <v>119</v>
       </c>
@@ -9668,7 +9665,7 @@
       <c r="U79" s="5"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="54"/>
+      <c r="A80" s="52"/>
       <c r="B80" s="49" t="s">
         <v>120</v>
       </c>
@@ -9695,7 +9692,7 @@
       <c r="U80" s="5"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="50">
+      <c r="A81" s="62">
         <v>12</v>
       </c>
       <c r="B81" s="47" t="s">
@@ -9704,191 +9701,191 @@
       <c r="C81" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="55" t="s">
+      <c r="D81" s="71" t="s">
         <v>122</v>
       </c>
-      <c r="E81" s="56"/>
-      <c r="F81" s="56"/>
-      <c r="G81" s="56"/>
-      <c r="H81" s="56"/>
-      <c r="I81" s="56"/>
-      <c r="J81" s="56"/>
-      <c r="K81" s="56"/>
-      <c r="L81" s="56"/>
-      <c r="M81" s="56"/>
-      <c r="N81" s="56"/>
-      <c r="O81" s="56"/>
-      <c r="P81" s="56"/>
-      <c r="Q81" s="56"/>
-      <c r="R81" s="56"/>
-      <c r="S81" s="56"/>
-      <c r="T81" s="56"/>
-      <c r="U81" s="57"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="72"/>
+      <c r="H81" s="72"/>
+      <c r="I81" s="72"/>
+      <c r="J81" s="72"/>
+      <c r="K81" s="72"/>
+      <c r="L81" s="72"/>
+      <c r="M81" s="72"/>
+      <c r="N81" s="72"/>
+      <c r="O81" s="72"/>
+      <c r="P81" s="72"/>
+      <c r="Q81" s="72"/>
+      <c r="R81" s="72"/>
+      <c r="S81" s="72"/>
+      <c r="T81" s="72"/>
+      <c r="U81" s="73"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="50"/>
+      <c r="A82" s="62"/>
       <c r="B82" s="47" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="58"/>
-      <c r="E82" s="59"/>
-      <c r="F82" s="59"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="59"/>
-      <c r="J82" s="59"/>
-      <c r="K82" s="59"/>
-      <c r="L82" s="59"/>
-      <c r="M82" s="59"/>
-      <c r="N82" s="59"/>
-      <c r="O82" s="59"/>
-      <c r="P82" s="59"/>
-      <c r="Q82" s="59"/>
-      <c r="R82" s="59"/>
-      <c r="S82" s="59"/>
-      <c r="T82" s="59"/>
-      <c r="U82" s="60"/>
+      <c r="D82" s="74"/>
+      <c r="E82" s="75"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="75"/>
+      <c r="I82" s="75"/>
+      <c r="J82" s="75"/>
+      <c r="K82" s="75"/>
+      <c r="L82" s="75"/>
+      <c r="M82" s="75"/>
+      <c r="N82" s="75"/>
+      <c r="O82" s="75"/>
+      <c r="P82" s="75"/>
+      <c r="Q82" s="75"/>
+      <c r="R82" s="75"/>
+      <c r="S82" s="75"/>
+      <c r="T82" s="75"/>
+      <c r="U82" s="76"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="50"/>
+      <c r="A83" s="62"/>
       <c r="B83" s="47" t="s">
         <v>124</v>
       </c>
       <c r="C83" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D83" s="58"/>
-      <c r="E83" s="59"/>
-      <c r="F83" s="59"/>
-      <c r="G83" s="59"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="59"/>
-      <c r="J83" s="59"/>
-      <c r="K83" s="59"/>
-      <c r="L83" s="59"/>
-      <c r="M83" s="59"/>
-      <c r="N83" s="59"/>
-      <c r="O83" s="59"/>
-      <c r="P83" s="59"/>
-      <c r="Q83" s="59"/>
-      <c r="R83" s="59"/>
-      <c r="S83" s="59"/>
-      <c r="T83" s="59"/>
-      <c r="U83" s="60"/>
+      <c r="D83" s="74"/>
+      <c r="E83" s="75"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="75"/>
+      <c r="I83" s="75"/>
+      <c r="J83" s="75"/>
+      <c r="K83" s="75"/>
+      <c r="L83" s="75"/>
+      <c r="M83" s="75"/>
+      <c r="N83" s="75"/>
+      <c r="O83" s="75"/>
+      <c r="P83" s="75"/>
+      <c r="Q83" s="75"/>
+      <c r="R83" s="75"/>
+      <c r="S83" s="75"/>
+      <c r="T83" s="75"/>
+      <c r="U83" s="76"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="50"/>
+      <c r="A84" s="62"/>
       <c r="B84" s="47" t="s">
         <v>125</v>
       </c>
       <c r="C84" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D84" s="58"/>
-      <c r="E84" s="59"/>
-      <c r="F84" s="59"/>
-      <c r="G84" s="59"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="59"/>
-      <c r="J84" s="59"/>
-      <c r="K84" s="59"/>
-      <c r="L84" s="59"/>
-      <c r="M84" s="59"/>
-      <c r="N84" s="59"/>
-      <c r="O84" s="59"/>
-      <c r="P84" s="59"/>
-      <c r="Q84" s="59"/>
-      <c r="R84" s="59"/>
-      <c r="S84" s="59"/>
-      <c r="T84" s="59"/>
-      <c r="U84" s="60"/>
+      <c r="D84" s="74"/>
+      <c r="E84" s="75"/>
+      <c r="F84" s="75"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="75"/>
+      <c r="I84" s="75"/>
+      <c r="J84" s="75"/>
+      <c r="K84" s="75"/>
+      <c r="L84" s="75"/>
+      <c r="M84" s="75"/>
+      <c r="N84" s="75"/>
+      <c r="O84" s="75"/>
+      <c r="P84" s="75"/>
+      <c r="Q84" s="75"/>
+      <c r="R84" s="75"/>
+      <c r="S84" s="75"/>
+      <c r="T84" s="75"/>
+      <c r="U84" s="76"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="50"/>
+      <c r="A85" s="62"/>
       <c r="B85" s="47" t="s">
         <v>126</v>
       </c>
       <c r="C85" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="58"/>
-      <c r="E85" s="59"/>
-      <c r="F85" s="59"/>
-      <c r="G85" s="59"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="59"/>
-      <c r="J85" s="59"/>
-      <c r="K85" s="59"/>
-      <c r="L85" s="59"/>
-      <c r="M85" s="59"/>
-      <c r="N85" s="59"/>
-      <c r="O85" s="59"/>
-      <c r="P85" s="59"/>
-      <c r="Q85" s="59"/>
-      <c r="R85" s="59"/>
-      <c r="S85" s="59"/>
-      <c r="T85" s="59"/>
-      <c r="U85" s="60"/>
+      <c r="D85" s="74"/>
+      <c r="E85" s="75"/>
+      <c r="F85" s="75"/>
+      <c r="G85" s="75"/>
+      <c r="H85" s="75"/>
+      <c r="I85" s="75"/>
+      <c r="J85" s="75"/>
+      <c r="K85" s="75"/>
+      <c r="L85" s="75"/>
+      <c r="M85" s="75"/>
+      <c r="N85" s="75"/>
+      <c r="O85" s="75"/>
+      <c r="P85" s="75"/>
+      <c r="Q85" s="75"/>
+      <c r="R85" s="75"/>
+      <c r="S85" s="75"/>
+      <c r="T85" s="75"/>
+      <c r="U85" s="76"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="50"/>
+      <c r="A86" s="62"/>
       <c r="B86" s="47" t="s">
         <v>127</v>
       </c>
       <c r="C86" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D86" s="58"/>
-      <c r="E86" s="59"/>
-      <c r="F86" s="59"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="59"/>
-      <c r="J86" s="59"/>
-      <c r="K86" s="59"/>
-      <c r="L86" s="59"/>
-      <c r="M86" s="59"/>
-      <c r="N86" s="59"/>
-      <c r="O86" s="59"/>
-      <c r="P86" s="59"/>
-      <c r="Q86" s="59"/>
-      <c r="R86" s="59"/>
-      <c r="S86" s="59"/>
-      <c r="T86" s="59"/>
-      <c r="U86" s="60"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="75"/>
+      <c r="F86" s="75"/>
+      <c r="G86" s="75"/>
+      <c r="H86" s="75"/>
+      <c r="I86" s="75"/>
+      <c r="J86" s="75"/>
+      <c r="K86" s="75"/>
+      <c r="L86" s="75"/>
+      <c r="M86" s="75"/>
+      <c r="N86" s="75"/>
+      <c r="O86" s="75"/>
+      <c r="P86" s="75"/>
+      <c r="Q86" s="75"/>
+      <c r="R86" s="75"/>
+      <c r="S86" s="75"/>
+      <c r="T86" s="75"/>
+      <c r="U86" s="76"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="50"/>
+      <c r="A87" s="62"/>
       <c r="B87" s="47" t="s">
         <v>128</v>
       </c>
       <c r="C87" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D87" s="58"/>
-      <c r="E87" s="59"/>
-      <c r="F87" s="59"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="59"/>
-      <c r="J87" s="59"/>
-      <c r="K87" s="59"/>
-      <c r="L87" s="59"/>
-      <c r="M87" s="59"/>
-      <c r="N87" s="59"/>
-      <c r="O87" s="59"/>
-      <c r="P87" s="59"/>
-      <c r="Q87" s="59"/>
-      <c r="R87" s="59"/>
-      <c r="S87" s="59"/>
-      <c r="T87" s="59"/>
-      <c r="U87" s="60"/>
+      <c r="D87" s="74"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="75"/>
+      <c r="G87" s="75"/>
+      <c r="H87" s="75"/>
+      <c r="I87" s="75"/>
+      <c r="J87" s="75"/>
+      <c r="K87" s="75"/>
+      <c r="L87" s="75"/>
+      <c r="M87" s="75"/>
+      <c r="N87" s="75"/>
+      <c r="O87" s="75"/>
+      <c r="P87" s="75"/>
+      <c r="Q87" s="75"/>
+      <c r="R87" s="75"/>
+      <c r="S87" s="75"/>
+      <c r="T87" s="75"/>
+      <c r="U87" s="76"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="54">
+      <c r="A88" s="52">
         <v>13</v>
       </c>
       <c r="B88" s="49" t="s">
@@ -9897,189 +9894,189 @@
       <c r="C88" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="58"/>
-      <c r="E88" s="59"/>
-      <c r="F88" s="59"/>
-      <c r="G88" s="59"/>
-      <c r="H88" s="59"/>
-      <c r="I88" s="59"/>
-      <c r="J88" s="59"/>
-      <c r="K88" s="59"/>
-      <c r="L88" s="59"/>
-      <c r="M88" s="59"/>
-      <c r="N88" s="59"/>
-      <c r="O88" s="59"/>
-      <c r="P88" s="59"/>
-      <c r="Q88" s="59"/>
-      <c r="R88" s="59"/>
-      <c r="S88" s="59"/>
-      <c r="T88" s="59"/>
-      <c r="U88" s="60"/>
+      <c r="D88" s="74"/>
+      <c r="E88" s="75"/>
+      <c r="F88" s="75"/>
+      <c r="G88" s="75"/>
+      <c r="H88" s="75"/>
+      <c r="I88" s="75"/>
+      <c r="J88" s="75"/>
+      <c r="K88" s="75"/>
+      <c r="L88" s="75"/>
+      <c r="M88" s="75"/>
+      <c r="N88" s="75"/>
+      <c r="O88" s="75"/>
+      <c r="P88" s="75"/>
+      <c r="Q88" s="75"/>
+      <c r="R88" s="75"/>
+      <c r="S88" s="75"/>
+      <c r="T88" s="75"/>
+      <c r="U88" s="76"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="54"/>
+      <c r="A89" s="52"/>
       <c r="B89" s="49" t="s">
         <v>130</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="58"/>
-      <c r="E89" s="59"/>
-      <c r="F89" s="59"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="59"/>
-      <c r="I89" s="59"/>
-      <c r="J89" s="59"/>
-      <c r="K89" s="59"/>
-      <c r="L89" s="59"/>
-      <c r="M89" s="59"/>
-      <c r="N89" s="59"/>
-      <c r="O89" s="59"/>
-      <c r="P89" s="59"/>
-      <c r="Q89" s="59"/>
-      <c r="R89" s="59"/>
-      <c r="S89" s="59"/>
-      <c r="T89" s="59"/>
-      <c r="U89" s="60"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="75"/>
+      <c r="F89" s="75"/>
+      <c r="G89" s="75"/>
+      <c r="H89" s="75"/>
+      <c r="I89" s="75"/>
+      <c r="J89" s="75"/>
+      <c r="K89" s="75"/>
+      <c r="L89" s="75"/>
+      <c r="M89" s="75"/>
+      <c r="N89" s="75"/>
+      <c r="O89" s="75"/>
+      <c r="P89" s="75"/>
+      <c r="Q89" s="75"/>
+      <c r="R89" s="75"/>
+      <c r="S89" s="75"/>
+      <c r="T89" s="75"/>
+      <c r="U89" s="76"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="54"/>
+      <c r="A90" s="52"/>
       <c r="B90" s="49" t="s">
         <v>131</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D90" s="58"/>
-      <c r="E90" s="59"/>
-      <c r="F90" s="59"/>
-      <c r="G90" s="59"/>
-      <c r="H90" s="59"/>
-      <c r="I90" s="59"/>
-      <c r="J90" s="59"/>
-      <c r="K90" s="59"/>
-      <c r="L90" s="59"/>
-      <c r="M90" s="59"/>
-      <c r="N90" s="59"/>
-      <c r="O90" s="59"/>
-      <c r="P90" s="59"/>
-      <c r="Q90" s="59"/>
-      <c r="R90" s="59"/>
-      <c r="S90" s="59"/>
-      <c r="T90" s="59"/>
-      <c r="U90" s="60"/>
+      <c r="D90" s="74"/>
+      <c r="E90" s="75"/>
+      <c r="F90" s="75"/>
+      <c r="G90" s="75"/>
+      <c r="H90" s="75"/>
+      <c r="I90" s="75"/>
+      <c r="J90" s="75"/>
+      <c r="K90" s="75"/>
+      <c r="L90" s="75"/>
+      <c r="M90" s="75"/>
+      <c r="N90" s="75"/>
+      <c r="O90" s="75"/>
+      <c r="P90" s="75"/>
+      <c r="Q90" s="75"/>
+      <c r="R90" s="75"/>
+      <c r="S90" s="75"/>
+      <c r="T90" s="75"/>
+      <c r="U90" s="76"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="54"/>
+      <c r="A91" s="52"/>
       <c r="B91" s="49" t="s">
         <v>132</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D91" s="58"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="59"/>
-      <c r="G91" s="59"/>
-      <c r="H91" s="59"/>
-      <c r="I91" s="59"/>
-      <c r="J91" s="59"/>
-      <c r="K91" s="59"/>
-      <c r="L91" s="59"/>
-      <c r="M91" s="59"/>
-      <c r="N91" s="59"/>
-      <c r="O91" s="59"/>
-      <c r="P91" s="59"/>
-      <c r="Q91" s="59"/>
-      <c r="R91" s="59"/>
-      <c r="S91" s="59"/>
-      <c r="T91" s="59"/>
-      <c r="U91" s="60"/>
+      <c r="D91" s="74"/>
+      <c r="E91" s="75"/>
+      <c r="F91" s="75"/>
+      <c r="G91" s="75"/>
+      <c r="H91" s="75"/>
+      <c r="I91" s="75"/>
+      <c r="J91" s="75"/>
+      <c r="K91" s="75"/>
+      <c r="L91" s="75"/>
+      <c r="M91" s="75"/>
+      <c r="N91" s="75"/>
+      <c r="O91" s="75"/>
+      <c r="P91" s="75"/>
+      <c r="Q91" s="75"/>
+      <c r="R91" s="75"/>
+      <c r="S91" s="75"/>
+      <c r="T91" s="75"/>
+      <c r="U91" s="76"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="54"/>
+      <c r="A92" s="52"/>
       <c r="B92" s="49" t="s">
         <v>133</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D92" s="58"/>
-      <c r="E92" s="59"/>
-      <c r="F92" s="59"/>
-      <c r="G92" s="59"/>
-      <c r="H92" s="59"/>
-      <c r="I92" s="59"/>
-      <c r="J92" s="59"/>
-      <c r="K92" s="59"/>
-      <c r="L92" s="59"/>
-      <c r="M92" s="59"/>
-      <c r="N92" s="59"/>
-      <c r="O92" s="59"/>
-      <c r="P92" s="59"/>
-      <c r="Q92" s="59"/>
-      <c r="R92" s="59"/>
-      <c r="S92" s="59"/>
-      <c r="T92" s="59"/>
-      <c r="U92" s="60"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="75"/>
+      <c r="F92" s="75"/>
+      <c r="G92" s="75"/>
+      <c r="H92" s="75"/>
+      <c r="I92" s="75"/>
+      <c r="J92" s="75"/>
+      <c r="K92" s="75"/>
+      <c r="L92" s="75"/>
+      <c r="M92" s="75"/>
+      <c r="N92" s="75"/>
+      <c r="O92" s="75"/>
+      <c r="P92" s="75"/>
+      <c r="Q92" s="75"/>
+      <c r="R92" s="75"/>
+      <c r="S92" s="75"/>
+      <c r="T92" s="75"/>
+      <c r="U92" s="76"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="54"/>
+      <c r="A93" s="52"/>
       <c r="B93" s="49" t="s">
         <v>134</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D93" s="58"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="59"/>
-      <c r="J93" s="59"/>
-      <c r="K93" s="59"/>
-      <c r="L93" s="59"/>
-      <c r="M93" s="59"/>
-      <c r="N93" s="59"/>
-      <c r="O93" s="59"/>
-      <c r="P93" s="59"/>
-      <c r="Q93" s="59"/>
-      <c r="R93" s="59"/>
-      <c r="S93" s="59"/>
-      <c r="T93" s="59"/>
-      <c r="U93" s="60"/>
+      <c r="D93" s="74"/>
+      <c r="E93" s="75"/>
+      <c r="F93" s="75"/>
+      <c r="G93" s="75"/>
+      <c r="H93" s="75"/>
+      <c r="I93" s="75"/>
+      <c r="J93" s="75"/>
+      <c r="K93" s="75"/>
+      <c r="L93" s="75"/>
+      <c r="M93" s="75"/>
+      <c r="N93" s="75"/>
+      <c r="O93" s="75"/>
+      <c r="P93" s="75"/>
+      <c r="Q93" s="75"/>
+      <c r="R93" s="75"/>
+      <c r="S93" s="75"/>
+      <c r="T93" s="75"/>
+      <c r="U93" s="76"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="54"/>
+      <c r="A94" s="52"/>
       <c r="B94" s="49" t="s">
         <v>135</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D94" s="61"/>
-      <c r="E94" s="62"/>
-      <c r="F94" s="62"/>
-      <c r="G94" s="62"/>
-      <c r="H94" s="62"/>
-      <c r="I94" s="62"/>
-      <c r="J94" s="62"/>
-      <c r="K94" s="62"/>
-      <c r="L94" s="62"/>
-      <c r="M94" s="62"/>
-      <c r="N94" s="62"/>
-      <c r="O94" s="62"/>
-      <c r="P94" s="62"/>
-      <c r="Q94" s="62"/>
-      <c r="R94" s="62"/>
-      <c r="S94" s="62"/>
-      <c r="T94" s="62"/>
-      <c r="U94" s="63"/>
+      <c r="D94" s="77"/>
+      <c r="E94" s="78"/>
+      <c r="F94" s="78"/>
+      <c r="G94" s="78"/>
+      <c r="H94" s="78"/>
+      <c r="I94" s="78"/>
+      <c r="J94" s="78"/>
+      <c r="K94" s="78"/>
+      <c r="L94" s="78"/>
+      <c r="M94" s="78"/>
+      <c r="N94" s="78"/>
+      <c r="O94" s="78"/>
+      <c r="P94" s="78"/>
+      <c r="Q94" s="78"/>
+      <c r="R94" s="78"/>
+      <c r="S94" s="78"/>
+      <c r="T94" s="78"/>
+      <c r="U94" s="79"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="50">
+      <c r="A95" s="62">
         <v>14</v>
       </c>
       <c r="B95" s="47" t="s">
@@ -10112,7 +10109,7 @@
       <c r="U95" s="14"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="50"/>
+      <c r="A96" s="62"/>
       <c r="B96" s="47" t="s">
         <v>138</v>
       </c>
@@ -10143,7 +10140,7 @@
       <c r="U96" s="14"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="50"/>
+      <c r="A97" s="62"/>
       <c r="B97" s="47" t="s">
         <v>139</v>
       </c>
@@ -10174,7 +10171,7 @@
       <c r="U97" s="14"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="50"/>
+      <c r="A98" s="62"/>
       <c r="B98" s="47" t="s">
         <v>140</v>
       </c>
@@ -10205,7 +10202,7 @@
       <c r="U98" s="14"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="50"/>
+      <c r="A99" s="62"/>
       <c r="B99" s="47" t="s">
         <v>141</v>
       </c>
@@ -10236,7 +10233,7 @@
       <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="50"/>
+      <c r="A100" s="62"/>
       <c r="B100" s="47" t="s">
         <v>142</v>
       </c>
@@ -10267,7 +10264,7 @@
       <c r="U100" s="14"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="50"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="47" t="s">
         <v>143</v>
       </c>
@@ -10298,7 +10295,7 @@
       <c r="U101" s="14"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="54">
+      <c r="A102" s="52">
         <v>15</v>
       </c>
       <c r="B102" s="49" t="s">
@@ -10331,7 +10328,7 @@
       <c r="U102" s="5"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="54"/>
+      <c r="A103" s="52"/>
       <c r="B103" s="49" t="s">
         <v>145</v>
       </c>
@@ -10362,7 +10359,7 @@
       <c r="U103" s="5"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="54"/>
+      <c r="A104" s="52"/>
       <c r="B104" s="49" t="s">
         <v>146</v>
       </c>
@@ -10393,7 +10390,7 @@
       <c r="U104" s="5"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="54"/>
+      <c r="A105" s="52"/>
       <c r="B105" s="49" t="s">
         <v>147</v>
       </c>
@@ -10424,7 +10421,7 @@
       <c r="U105" s="5"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="54"/>
+      <c r="A106" s="52"/>
       <c r="B106" s="49" t="s">
         <v>148</v>
       </c>
@@ -10455,7 +10452,7 @@
       <c r="U106" s="5"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="54"/>
+      <c r="A107" s="52"/>
       <c r="B107" s="49" t="s">
         <v>149</v>
       </c>
@@ -10486,7 +10483,7 @@
       <c r="U107" s="5"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="54"/>
+      <c r="A108" s="52"/>
       <c r="B108" s="49" t="s">
         <v>150</v>
       </c>
@@ -10517,7 +10514,7 @@
       <c r="U108" s="5"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="50">
+      <c r="A109" s="62">
         <v>16</v>
       </c>
       <c r="B109" s="47" t="s">
@@ -10550,7 +10547,7 @@
       <c r="U109" s="15"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="50"/>
+      <c r="A110" s="62"/>
       <c r="B110" s="47" t="s">
         <v>152</v>
       </c>
@@ -10581,7 +10578,7 @@
       <c r="U110" s="15"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="50"/>
+      <c r="A111" s="62"/>
       <c r="B111" s="47" t="s">
         <v>153</v>
       </c>
@@ -10612,7 +10609,7 @@
       <c r="U111" s="15"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="50"/>
+      <c r="A112" s="62"/>
       <c r="B112" s="47" t="s">
         <v>154</v>
       </c>
@@ -10643,7 +10640,7 @@
       <c r="U112" s="15"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="50"/>
+      <c r="A113" s="62"/>
       <c r="B113" s="47" t="s">
         <v>155</v>
       </c>
@@ -10674,7 +10671,7 @@
       <c r="U113" s="15"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="50"/>
+      <c r="A114" s="62"/>
       <c r="B114" s="47" t="s">
         <v>156</v>
       </c>
@@ -10705,7 +10702,7 @@
       <c r="U114" s="15"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="50"/>
+      <c r="A115" s="62"/>
       <c r="B115" s="47" t="s">
         <v>157</v>
       </c>
@@ -10736,7 +10733,7 @@
       <c r="U115" s="15"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="54">
+      <c r="A116" s="52">
         <v>17</v>
       </c>
       <c r="B116" s="49" t="s">
@@ -10769,7 +10766,7 @@
       <c r="U116" s="5"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="54"/>
+      <c r="A117" s="52"/>
       <c r="B117" s="49" t="s">
         <v>159</v>
       </c>
@@ -10800,7 +10797,7 @@
       <c r="U117" s="5"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="54"/>
+      <c r="A118" s="52"/>
       <c r="B118" s="49" t="s">
         <v>160</v>
       </c>
@@ -10831,7 +10828,7 @@
       <c r="U118" s="5"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="54"/>
+      <c r="A119" s="52"/>
       <c r="B119" s="49" t="s">
         <v>161</v>
       </c>
@@ -10862,7 +10859,7 @@
       <c r="U119" s="5"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="54"/>
+      <c r="A120" s="52"/>
       <c r="B120" s="49" t="s">
         <v>162</v>
       </c>
@@ -10893,7 +10890,7 @@
       <c r="U120" s="5"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="54"/>
+      <c r="A121" s="52"/>
       <c r="B121" s="49" t="s">
         <v>163</v>
       </c>
@@ -10924,7 +10921,7 @@
       <c r="U121" s="5"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="54"/>
+      <c r="A122" s="52"/>
       <c r="B122" s="49" t="s">
         <v>164</v>
       </c>
@@ -10955,7 +10952,7 @@
       <c r="U122" s="5"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="50">
+      <c r="A123" s="62">
         <v>18</v>
       </c>
       <c r="B123" s="47" t="s">
@@ -10988,7 +10985,7 @@
       <c r="U123" s="15"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="50"/>
+      <c r="A124" s="62"/>
       <c r="B124" s="47" t="s">
         <v>166</v>
       </c>
@@ -11019,7 +11016,7 @@
       <c r="U124" s="15"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="50"/>
+      <c r="A125" s="62"/>
       <c r="B125" s="47" t="s">
         <v>167</v>
       </c>
@@ -11050,7 +11047,7 @@
       <c r="U125" s="15"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="50"/>
+      <c r="A126" s="62"/>
       <c r="B126" s="47" t="s">
         <v>168</v>
       </c>
@@ -11081,36 +11078,36 @@
       <c r="U126" s="15"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="50"/>
+      <c r="A127" s="62"/>
       <c r="B127" s="46" t="s">
         <v>169</v>
       </c>
       <c r="C127" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="D127" s="51" t="s">
+      <c r="D127" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="E127" s="52"/>
-      <c r="F127" s="52"/>
-      <c r="G127" s="52"/>
-      <c r="H127" s="52"/>
-      <c r="I127" s="52"/>
-      <c r="J127" s="52"/>
-      <c r="K127" s="52"/>
-      <c r="L127" s="52"/>
-      <c r="M127" s="52"/>
-      <c r="N127" s="52"/>
-      <c r="O127" s="52"/>
-      <c r="P127" s="52"/>
-      <c r="Q127" s="52"/>
-      <c r="R127" s="52"/>
-      <c r="S127" s="52"/>
-      <c r="T127" s="52"/>
-      <c r="U127" s="53"/>
+      <c r="E127" s="69"/>
+      <c r="F127" s="69"/>
+      <c r="G127" s="69"/>
+      <c r="H127" s="69"/>
+      <c r="I127" s="69"/>
+      <c r="J127" s="69"/>
+      <c r="K127" s="69"/>
+      <c r="L127" s="69"/>
+      <c r="M127" s="69"/>
+      <c r="N127" s="69"/>
+      <c r="O127" s="69"/>
+      <c r="P127" s="69"/>
+      <c r="Q127" s="69"/>
+      <c r="R127" s="69"/>
+      <c r="S127" s="69"/>
+      <c r="T127" s="69"/>
+      <c r="U127" s="70"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="50"/>
+      <c r="A128" s="62"/>
       <c r="B128" s="47" t="s">
         <v>171</v>
       </c>
@@ -11141,7 +11138,7 @@
       <c r="U128" s="15"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="50"/>
+      <c r="A129" s="62"/>
       <c r="B129" s="47" t="s">
         <v>172</v>
       </c>
@@ -11172,7 +11169,7 @@
       <c r="U129" s="15"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="54">
+      <c r="A130" s="52">
         <v>19</v>
       </c>
       <c r="B130" s="49" t="s">
@@ -11205,7 +11202,7 @@
       <c r="U130" s="5"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="54"/>
+      <c r="A131" s="52"/>
       <c r="B131" s="49" t="s">
         <v>174</v>
       </c>
@@ -11236,7 +11233,7 @@
       <c r="U131" s="5"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="54"/>
+      <c r="A132" s="52"/>
       <c r="B132" s="49" t="s">
         <v>175</v>
       </c>
@@ -11267,7 +11264,7 @@
       <c r="U132" s="5"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="54"/>
+      <c r="A133" s="52"/>
       <c r="B133" s="49" t="s">
         <v>176</v>
       </c>
@@ -11298,7 +11295,7 @@
       <c r="U133" s="5"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="54"/>
+      <c r="A134" s="52"/>
       <c r="B134" s="49" t="s">
         <v>177</v>
       </c>
@@ -11329,7 +11326,7 @@
       <c r="U134" s="5"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="54"/>
+      <c r="A135" s="52"/>
       <c r="B135" s="49" t="s">
         <v>178</v>
       </c>
@@ -11360,7 +11357,7 @@
       <c r="U135" s="5"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="54"/>
+      <c r="A136" s="52"/>
       <c r="B136" s="49" t="s">
         <v>179</v>
       </c>
@@ -11406,6 +11403,27 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="D29:U31"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
@@ -11422,27 +11440,6 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11485,81 +11482,81 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="75" t="s">
+      <c r="B2" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="73" t="s">
+      <c r="C2" s="65"/>
+      <c r="D2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="73"/>
-      <c r="F2" s="73"/>
-      <c r="G2" s="73" t="s">
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="73"/>
-      <c r="I2" s="73"/>
-      <c r="J2" s="73" t="s">
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
-      <c r="M2" s="73" t="s">
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="73"/>
-      <c r="O2" s="73"/>
-      <c r="P2" s="73" t="s">
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="73"/>
-      <c r="R2" s="73"/>
-      <c r="S2" s="73" t="s">
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="T2" s="73"/>
-      <c r="U2" s="73"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
     </row>
     <row r="3" spans="1:27" s="1" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A3" s="73"/>
-      <c r="B3" s="77"/>
-      <c r="C3" s="78"/>
-      <c r="D3" s="74" t="s">
+      <c r="A3" s="51"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67"/>
+      <c r="D3" s="63" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="74"/>
-      <c r="F3" s="74"/>
-      <c r="G3" s="73" t="s">
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
+      <c r="G3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="73" t="s">
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="K3" s="73"/>
-      <c r="L3" s="73"/>
-      <c r="M3" s="73" t="s">
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="N3" s="73"/>
-      <c r="O3" s="73"/>
-      <c r="P3" s="73" t="s">
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="73"/>
-      <c r="R3" s="73"/>
-      <c r="S3" s="73" t="s">
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="T3" s="73"/>
-      <c r="U3" s="73"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
     </row>
     <row r="4" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A4" s="54">
+      <c r="A4" s="52">
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
@@ -11599,7 +11596,7 @@
       </c>
     </row>
     <row r="5" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A5" s="54"/>
+      <c r="A5" s="52"/>
       <c r="B5" s="2" t="s">
         <v>23</v>
       </c>
@@ -11663,7 +11660,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A6" s="54"/>
+      <c r="A6" s="52"/>
       <c r="B6" s="2" t="s">
         <v>29</v>
       </c>
@@ -11727,7 +11724,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A7" s="54"/>
+      <c r="A7" s="52"/>
       <c r="B7" s="2" t="s">
         <v>34</v>
       </c>
@@ -11789,7 +11786,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A8" s="54"/>
+      <c r="A8" s="52"/>
       <c r="B8" s="2" t="s">
         <v>39</v>
       </c>
@@ -11853,7 +11850,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="54"/>
+      <c r="A9" s="52"/>
       <c r="B9" s="2" t="s">
         <v>41</v>
       </c>
@@ -11895,7 +11892,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A10" s="54"/>
+      <c r="A10" s="52"/>
       <c r="B10" s="2" t="s">
         <v>44</v>
       </c>
@@ -11939,7 +11936,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="50">
+      <c r="A11" s="62">
         <v>2</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -11985,7 +11982,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="50"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="11" t="s">
         <v>48</v>
       </c>
@@ -12047,7 +12044,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="50"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="11" t="s">
         <v>49</v>
       </c>
@@ -12099,7 +12096,7 @@
       <c r="AA13" s="10"/>
     </row>
     <row r="14" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="50"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="11" t="s">
         <v>50</v>
       </c>
@@ -12163,7 +12160,7 @@
       <c r="AA14" s="10"/>
     </row>
     <row r="15" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="50"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="11" t="s">
         <v>54</v>
       </c>
@@ -12210,7 +12207,7 @@
       <c r="U15" s="14"/>
     </row>
     <row r="16" spans="1:27" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="50"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="11" t="s">
         <v>55</v>
       </c>
@@ -12237,7 +12234,7 @@
       <c r="U16" s="14"/>
     </row>
     <row r="17" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="50"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="11" t="s">
         <v>56</v>
       </c>
@@ -12264,7 +12261,7 @@
       <c r="U17" s="14"/>
     </row>
     <row r="18" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="54">
+      <c r="A18" s="52">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -12295,7 +12292,7 @@
       <c r="U18" s="5"/>
     </row>
     <row r="19" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="54"/>
+      <c r="A19" s="52"/>
       <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
@@ -12342,7 +12339,7 @@
       <c r="U19" s="5"/>
     </row>
     <row r="20" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="54"/>
+      <c r="A20" s="52"/>
       <c r="B20" s="2" t="s">
         <v>59</v>
       </c>
@@ -12389,7 +12386,7 @@
       <c r="U20" s="5"/>
     </row>
     <row r="21" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="54"/>
+      <c r="A21" s="52"/>
       <c r="B21" s="2" t="s">
         <v>60</v>
       </c>
@@ -12448,7 +12445,7 @@
       </c>
     </row>
     <row r="22" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="54"/>
+      <c r="A22" s="52"/>
       <c r="B22" s="2" t="s">
         <v>61</v>
       </c>
@@ -12495,7 +12492,7 @@
       <c r="U22" s="5"/>
     </row>
     <row r="23" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="54"/>
+      <c r="A23" s="52"/>
       <c r="B23" s="2" t="s">
         <v>62</v>
       </c>
@@ -12522,7 +12519,7 @@
       <c r="U23" s="5"/>
     </row>
     <row r="24" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="54"/>
+      <c r="A24" s="52"/>
       <c r="B24" s="16" t="s">
         <v>63</v>
       </c>
@@ -12549,7 +12546,7 @@
       <c r="U24" s="19"/>
     </row>
     <row r="25" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="50">
+      <c r="A25" s="62">
         <v>4</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -12580,7 +12577,7 @@
       <c r="U25" s="14"/>
     </row>
     <row r="26" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="50"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="11" t="s">
         <v>65</v>
       </c>
@@ -12627,7 +12624,7 @@
       <c r="U26" s="14"/>
     </row>
     <row r="27" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="50"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="11" t="s">
         <v>66</v>
       </c>
@@ -12674,7 +12671,7 @@
       <c r="U27" s="14"/>
     </row>
     <row r="28" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="50"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="11" t="s">
         <v>67</v>
       </c>
@@ -12721,90 +12718,90 @@
       <c r="U28" s="14"/>
     </row>
     <row r="29" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="50"/>
+      <c r="A29" s="62"/>
       <c r="B29" s="23" t="s">
         <v>68</v>
       </c>
       <c r="C29" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D29" s="64" t="s">
+      <c r="D29" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="65"/>
-      <c r="J29" s="65"/>
-      <c r="K29" s="65"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="65"/>
-      <c r="S29" s="65"/>
-      <c r="T29" s="65"/>
-      <c r="U29" s="66"/>
+      <c r="E29" s="54"/>
+      <c r="F29" s="54"/>
+      <c r="G29" s="54"/>
+      <c r="H29" s="54"/>
+      <c r="I29" s="54"/>
+      <c r="J29" s="54"/>
+      <c r="K29" s="54"/>
+      <c r="L29" s="54"/>
+      <c r="M29" s="54"/>
+      <c r="N29" s="54"/>
+      <c r="O29" s="54"/>
+      <c r="P29" s="54"/>
+      <c r="Q29" s="54"/>
+      <c r="R29" s="54"/>
+      <c r="S29" s="54"/>
+      <c r="T29" s="54"/>
+      <c r="U29" s="55"/>
     </row>
     <row r="30" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="50"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="23" t="s">
         <v>70</v>
       </c>
       <c r="C30" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D30" s="67"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
-      <c r="M30" s="68"/>
-      <c r="N30" s="68"/>
-      <c r="O30" s="68"/>
-      <c r="P30" s="68"/>
-      <c r="Q30" s="68"/>
-      <c r="R30" s="68"/>
-      <c r="S30" s="68"/>
-      <c r="T30" s="68"/>
-      <c r="U30" s="69"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
+      <c r="J30" s="57"/>
+      <c r="K30" s="57"/>
+      <c r="L30" s="57"/>
+      <c r="M30" s="57"/>
+      <c r="N30" s="57"/>
+      <c r="O30" s="57"/>
+      <c r="P30" s="57"/>
+      <c r="Q30" s="57"/>
+      <c r="R30" s="57"/>
+      <c r="S30" s="57"/>
+      <c r="T30" s="57"/>
+      <c r="U30" s="58"/>
     </row>
     <row r="31" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="50"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="23" t="s">
         <v>71</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D31" s="70"/>
-      <c r="E31" s="71"/>
-      <c r="F31" s="71"/>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
-      <c r="I31" s="71"/>
-      <c r="J31" s="71"/>
-      <c r="K31" s="71"/>
-      <c r="L31" s="71"/>
-      <c r="M31" s="71"/>
-      <c r="N31" s="71"/>
-      <c r="O31" s="71"/>
-      <c r="P31" s="71"/>
-      <c r="Q31" s="71"/>
-      <c r="R31" s="71"/>
-      <c r="S31" s="71"/>
-      <c r="T31" s="71"/>
-      <c r="U31" s="72"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
+      <c r="J31" s="60"/>
+      <c r="K31" s="60"/>
+      <c r="L31" s="60"/>
+      <c r="M31" s="60"/>
+      <c r="N31" s="60"/>
+      <c r="O31" s="60"/>
+      <c r="P31" s="60"/>
+      <c r="Q31" s="60"/>
+      <c r="R31" s="60"/>
+      <c r="S31" s="60"/>
+      <c r="T31" s="60"/>
+      <c r="U31" s="61"/>
     </row>
     <row r="32" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="54">
+      <c r="A32" s="52">
         <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -12820,7 +12817,7 @@
         <v>32</v>
       </c>
       <c r="F32" s="45" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="G32" s="43" t="s">
         <v>31</v>
@@ -12829,7 +12826,7 @@
         <v>32</v>
       </c>
       <c r="I32" s="45" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="J32" s="43" t="s">
         <v>31</v>
@@ -12838,7 +12835,7 @@
         <v>32</v>
       </c>
       <c r="L32" s="45" t="s">
-        <v>186</v>
+        <v>27</v>
       </c>
       <c r="M32" s="2" t="s">
         <v>19</v>
@@ -12853,7 +12850,7 @@
       <c r="U32" s="5"/>
     </row>
     <row r="33" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="54"/>
+      <c r="A33" s="52"/>
       <c r="B33" s="2" t="s">
         <v>73</v>
       </c>
@@ -12900,7 +12897,7 @@
       <c r="U33" s="5"/>
     </row>
     <row r="34" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A34" s="54"/>
+      <c r="A34" s="52"/>
       <c r="B34" s="2" t="s">
         <v>74</v>
       </c>
@@ -12947,117 +12944,117 @@
       <c r="U34" s="5"/>
     </row>
     <row r="35" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="54"/>
+      <c r="A35" s="52"/>
       <c r="B35" s="46" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="64" t="s">
+      <c r="D35" s="53" t="s">
         <v>170</v>
       </c>
-      <c r="E35" s="65"/>
-      <c r="F35" s="65"/>
-      <c r="G35" s="65"/>
-      <c r="H35" s="65"/>
-      <c r="I35" s="65"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="65"/>
-      <c r="L35" s="65"/>
-      <c r="M35" s="65"/>
-      <c r="N35" s="65"/>
-      <c r="O35" s="65"/>
-      <c r="P35" s="65"/>
-      <c r="Q35" s="65"/>
-      <c r="R35" s="65"/>
-      <c r="S35" s="65"/>
-      <c r="T35" s="65"/>
-      <c r="U35" s="66"/>
+      <c r="E35" s="54"/>
+      <c r="F35" s="54"/>
+      <c r="G35" s="54"/>
+      <c r="H35" s="54"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
+      <c r="K35" s="54"/>
+      <c r="L35" s="54"/>
+      <c r="M35" s="54"/>
+      <c r="N35" s="54"/>
+      <c r="O35" s="54"/>
+      <c r="P35" s="54"/>
+      <c r="Q35" s="54"/>
+      <c r="R35" s="54"/>
+      <c r="S35" s="54"/>
+      <c r="T35" s="54"/>
+      <c r="U35" s="55"/>
     </row>
     <row r="36" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A36" s="54"/>
+      <c r="A36" s="52"/>
       <c r="B36" s="46" t="s">
         <v>76</v>
       </c>
       <c r="C36" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="D36" s="67"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="68"/>
-      <c r="M36" s="68"/>
-      <c r="N36" s="68"/>
-      <c r="O36" s="68"/>
-      <c r="P36" s="68"/>
-      <c r="Q36" s="68"/>
-      <c r="R36" s="68"/>
-      <c r="S36" s="68"/>
-      <c r="T36" s="68"/>
-      <c r="U36" s="69"/>
+      <c r="D36" s="56"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
+      <c r="J36" s="57"/>
+      <c r="K36" s="57"/>
+      <c r="L36" s="57"/>
+      <c r="M36" s="57"/>
+      <c r="N36" s="57"/>
+      <c r="O36" s="57"/>
+      <c r="P36" s="57"/>
+      <c r="Q36" s="57"/>
+      <c r="R36" s="57"/>
+      <c r="S36" s="57"/>
+      <c r="T36" s="57"/>
+      <c r="U36" s="58"/>
     </row>
     <row r="37" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="54"/>
+      <c r="A37" s="52"/>
       <c r="B37" s="46" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
-      <c r="L37" s="68"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="68"/>
-      <c r="O37" s="68"/>
-      <c r="P37" s="68"/>
-      <c r="Q37" s="68"/>
-      <c r="R37" s="68"/>
-      <c r="S37" s="68"/>
-      <c r="T37" s="68"/>
-      <c r="U37" s="69"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="57"/>
+      <c r="O37" s="57"/>
+      <c r="P37" s="57"/>
+      <c r="Q37" s="57"/>
+      <c r="R37" s="57"/>
+      <c r="S37" s="57"/>
+      <c r="T37" s="57"/>
+      <c r="U37" s="58"/>
     </row>
     <row r="38" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A38" s="54"/>
+      <c r="A38" s="52"/>
       <c r="B38" s="46" t="s">
         <v>78</v>
       </c>
       <c r="C38" s="24" t="s">
         <v>45</v>
       </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="68"/>
-      <c r="O38" s="68"/>
-      <c r="P38" s="68"/>
-      <c r="Q38" s="68"/>
-      <c r="R38" s="68"/>
-      <c r="S38" s="68"/>
-      <c r="T38" s="68"/>
-      <c r="U38" s="69"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="57"/>
+      <c r="O38" s="57"/>
+      <c r="P38" s="57"/>
+      <c r="Q38" s="57"/>
+      <c r="R38" s="57"/>
+      <c r="S38" s="57"/>
+      <c r="T38" s="57"/>
+      <c r="U38" s="58"/>
     </row>
     <row r="39" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A39" s="50">
+      <c r="A39" s="62">
         <v>6</v>
       </c>
       <c r="B39" s="46" t="s">
@@ -13066,81 +13063,81 @@
       <c r="C39" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="68"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="68"/>
-      <c r="O39" s="68"/>
-      <c r="P39" s="68"/>
-      <c r="Q39" s="68"/>
-      <c r="R39" s="68"/>
-      <c r="S39" s="68"/>
-      <c r="T39" s="68"/>
-      <c r="U39" s="69"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="57"/>
+      <c r="O39" s="57"/>
+      <c r="P39" s="57"/>
+      <c r="Q39" s="57"/>
+      <c r="R39" s="57"/>
+      <c r="S39" s="57"/>
+      <c r="T39" s="57"/>
+      <c r="U39" s="58"/>
     </row>
     <row r="40" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A40" s="50"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="46" t="s">
         <v>80</v>
       </c>
       <c r="C40" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="D40" s="67"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-      <c r="O40" s="68"/>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="68"/>
-      <c r="S40" s="68"/>
-      <c r="T40" s="68"/>
-      <c r="U40" s="69"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="57"/>
+      <c r="O40" s="57"/>
+      <c r="P40" s="57"/>
+      <c r="Q40" s="57"/>
+      <c r="R40" s="57"/>
+      <c r="S40" s="57"/>
+      <c r="T40" s="57"/>
+      <c r="U40" s="58"/>
     </row>
     <row r="41" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A41" s="50"/>
+      <c r="A41" s="62"/>
       <c r="B41" s="46" t="s">
         <v>81</v>
       </c>
       <c r="C41" s="24" t="s">
         <v>30</v>
       </c>
-      <c r="D41" s="70"/>
-      <c r="E41" s="71"/>
-      <c r="F41" s="71"/>
-      <c r="G41" s="71"/>
-      <c r="H41" s="71"/>
-      <c r="I41" s="71"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="71"/>
-      <c r="L41" s="71"/>
-      <c r="M41" s="71"/>
-      <c r="N41" s="71"/>
-      <c r="O41" s="71"/>
-      <c r="P41" s="71"/>
-      <c r="Q41" s="71"/>
-      <c r="R41" s="71"/>
-      <c r="S41" s="71"/>
-      <c r="T41" s="71"/>
-      <c r="U41" s="72"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
+      <c r="J41" s="60"/>
+      <c r="K41" s="60"/>
+      <c r="L41" s="60"/>
+      <c r="M41" s="60"/>
+      <c r="N41" s="60"/>
+      <c r="O41" s="60"/>
+      <c r="P41" s="60"/>
+      <c r="Q41" s="60"/>
+      <c r="R41" s="60"/>
+      <c r="S41" s="60"/>
+      <c r="T41" s="60"/>
+      <c r="U41" s="61"/>
     </row>
     <row r="42" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A42" s="50"/>
+      <c r="A42" s="62"/>
       <c r="B42" s="47" t="s">
         <v>82</v>
       </c>
@@ -13199,7 +13196,7 @@
       </c>
     </row>
     <row r="43" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="50"/>
+      <c r="A43" s="62"/>
       <c r="B43" s="47" t="s">
         <v>83</v>
       </c>
@@ -13246,7 +13243,7 @@
       <c r="U43" s="14"/>
     </row>
     <row r="44" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="50"/>
+      <c r="A44" s="62"/>
       <c r="B44" s="48" t="s">
         <v>84</v>
       </c>
@@ -13273,7 +13270,7 @@
       <c r="U44" s="19"/>
     </row>
     <row r="45" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="50"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="47" t="s">
         <v>85</v>
       </c>
@@ -13300,7 +13297,7 @@
       <c r="U45" s="14"/>
     </row>
     <row r="46" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="54">
+      <c r="A46" s="52">
         <v>7</v>
       </c>
       <c r="B46" s="49" t="s">
@@ -13331,7 +13328,7 @@
       <c r="U46" s="5"/>
     </row>
     <row r="47" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="54"/>
+      <c r="A47" s="52"/>
       <c r="B47" s="49" t="s">
         <v>87</v>
       </c>
@@ -13378,7 +13375,7 @@
       <c r="U47" s="5"/>
     </row>
     <row r="48" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="54"/>
+      <c r="A48" s="52"/>
       <c r="B48" s="49" t="s">
         <v>88</v>
       </c>
@@ -13425,7 +13422,7 @@
       <c r="U48" s="5"/>
     </row>
     <row r="49" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A49" s="54"/>
+      <c r="A49" s="52"/>
       <c r="B49" s="49" t="s">
         <v>89</v>
       </c>
@@ -13472,7 +13469,7 @@
       <c r="U49" s="5"/>
     </row>
     <row r="50" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A50" s="54"/>
+      <c r="A50" s="52"/>
       <c r="B50" s="49" t="s">
         <v>90</v>
       </c>
@@ -13519,7 +13516,7 @@
       <c r="U50" s="5"/>
     </row>
     <row r="51" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A51" s="54"/>
+      <c r="A51" s="52"/>
       <c r="B51" s="49" t="s">
         <v>91</v>
       </c>
@@ -13546,7 +13543,7 @@
       <c r="U51" s="5"/>
     </row>
     <row r="52" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A52" s="54"/>
+      <c r="A52" s="52"/>
       <c r="B52" s="49" t="s">
         <v>92</v>
       </c>
@@ -13573,7 +13570,7 @@
       <c r="U52" s="5"/>
     </row>
     <row r="53" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A53" s="50">
+      <c r="A53" s="62">
         <v>8</v>
       </c>
       <c r="B53" s="47" t="s">
@@ -13604,7 +13601,7 @@
       <c r="U53" s="14"/>
     </row>
     <row r="54" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A54" s="50"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="47" t="s">
         <v>94</v>
       </c>
@@ -13651,7 +13648,7 @@
       <c r="U54" s="14"/>
     </row>
     <row r="55" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A55" s="50"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="47" t="s">
         <v>95</v>
       </c>
@@ -13698,7 +13695,7 @@
       <c r="U55" s="14"/>
     </row>
     <row r="56" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A56" s="50"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="47" t="s">
         <v>96</v>
       </c>
@@ -13757,7 +13754,7 @@
       </c>
     </row>
     <row r="57" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A57" s="50"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="47" t="s">
         <v>97</v>
       </c>
@@ -13804,7 +13801,7 @@
       <c r="U57" s="14"/>
     </row>
     <row r="58" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="50"/>
+      <c r="A58" s="62"/>
       <c r="B58" s="47" t="s">
         <v>98</v>
       </c>
@@ -13831,7 +13828,7 @@
       <c r="U58" s="14"/>
     </row>
     <row r="59" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="50"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="47" t="s">
         <v>99</v>
       </c>
@@ -13858,7 +13855,7 @@
       <c r="U59" s="14"/>
     </row>
     <row r="60" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="54">
+      <c r="A60" s="52">
         <v>9</v>
       </c>
       <c r="B60" s="49" t="s">
@@ -13889,7 +13886,7 @@
       <c r="U60" s="5"/>
     </row>
     <row r="61" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="54"/>
+      <c r="A61" s="52"/>
       <c r="B61" s="49" t="s">
         <v>101</v>
       </c>
@@ -13936,7 +13933,7 @@
       <c r="U61" s="5"/>
     </row>
     <row r="62" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="54"/>
+      <c r="A62" s="52"/>
       <c r="B62" s="49" t="s">
         <v>102</v>
       </c>
@@ -13983,7 +13980,7 @@
       <c r="U62" s="5"/>
     </row>
     <row r="63" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="54"/>
+      <c r="A63" s="52"/>
       <c r="B63" s="49" t="s">
         <v>103</v>
       </c>
@@ -14042,7 +14039,7 @@
       </c>
     </row>
     <row r="64" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="54"/>
+      <c r="A64" s="52"/>
       <c r="B64" s="49" t="s">
         <v>104</v>
       </c>
@@ -14089,7 +14086,7 @@
       <c r="U64" s="6"/>
     </row>
     <row r="65" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A65" s="54"/>
+      <c r="A65" s="52"/>
       <c r="B65" s="49" t="s">
         <v>105</v>
       </c>
@@ -14116,7 +14113,7 @@
       <c r="U65" s="6"/>
     </row>
     <row r="66" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A66" s="54"/>
+      <c r="A66" s="52"/>
       <c r="B66" s="49" t="s">
         <v>106</v>
       </c>
@@ -14143,7 +14140,7 @@
       <c r="U66" s="6"/>
     </row>
     <row r="67" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A67" s="50">
+      <c r="A67" s="62">
         <v>10</v>
       </c>
       <c r="B67" s="47" t="s">
@@ -14174,7 +14171,7 @@
       <c r="U67" s="15"/>
     </row>
     <row r="68" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A68" s="50"/>
+      <c r="A68" s="62"/>
       <c r="B68" s="47" t="s">
         <v>108</v>
       </c>
@@ -14221,7 +14218,7 @@
       <c r="U68" s="15"/>
     </row>
     <row r="69" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="50"/>
+      <c r="A69" s="62"/>
       <c r="B69" s="47" t="s">
         <v>109</v>
       </c>
@@ -14268,7 +14265,7 @@
       <c r="U69" s="15"/>
     </row>
     <row r="70" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="50"/>
+      <c r="A70" s="62"/>
       <c r="B70" s="47" t="s">
         <v>110</v>
       </c>
@@ -14327,7 +14324,7 @@
       </c>
     </row>
     <row r="71" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="50"/>
+      <c r="A71" s="62"/>
       <c r="B71" s="47" t="s">
         <v>111</v>
       </c>
@@ -14374,7 +14371,7 @@
       <c r="U71" s="15"/>
     </row>
     <row r="72" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="50"/>
+      <c r="A72" s="62"/>
       <c r="B72" s="47" t="s">
         <v>112</v>
       </c>
@@ -14401,7 +14398,7 @@
       <c r="U72" s="15"/>
     </row>
     <row r="73" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="50"/>
+      <c r="A73" s="62"/>
       <c r="B73" s="47" t="s">
         <v>113</v>
       </c>
@@ -14428,7 +14425,7 @@
       <c r="U73" s="15"/>
     </row>
     <row r="74" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="54">
+      <c r="A74" s="52">
         <v>11</v>
       </c>
       <c r="B74" s="49" t="s">
@@ -14459,7 +14456,7 @@
       <c r="U74" s="6"/>
     </row>
     <row r="75" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="54"/>
+      <c r="A75" s="52"/>
       <c r="B75" s="49" t="s">
         <v>115</v>
       </c>
@@ -14506,7 +14503,7 @@
       <c r="U75" s="6"/>
     </row>
     <row r="76" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="54"/>
+      <c r="A76" s="52"/>
       <c r="B76" s="49" t="s">
         <v>116</v>
       </c>
@@ -14553,7 +14550,7 @@
       <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A77" s="54"/>
+      <c r="A77" s="52"/>
       <c r="B77" s="49" t="s">
         <v>117</v>
       </c>
@@ -14600,7 +14597,7 @@
       <c r="U77" s="5"/>
     </row>
     <row r="78" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A78" s="54"/>
+      <c r="A78" s="52"/>
       <c r="B78" s="49" t="s">
         <v>118</v>
       </c>
@@ -14647,7 +14644,7 @@
       <c r="U78" s="5"/>
     </row>
     <row r="79" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A79" s="54"/>
+      <c r="A79" s="52"/>
       <c r="B79" s="49" t="s">
         <v>119</v>
       </c>
@@ -14674,7 +14671,7 @@
       <c r="U79" s="5"/>
     </row>
     <row r="80" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="54"/>
+      <c r="A80" s="52"/>
       <c r="B80" s="49" t="s">
         <v>120</v>
       </c>
@@ -14701,7 +14698,7 @@
       <c r="U80" s="5"/>
     </row>
     <row r="81" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="50">
+      <c r="A81" s="62">
         <v>12</v>
       </c>
       <c r="B81" s="47" t="s">
@@ -14710,191 +14707,191 @@
       <c r="C81" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D81" s="55" t="s">
+      <c r="D81" s="71" t="s">
         <v>122</v>
       </c>
-      <c r="E81" s="56"/>
-      <c r="F81" s="56"/>
-      <c r="G81" s="56"/>
-      <c r="H81" s="56"/>
-      <c r="I81" s="56"/>
-      <c r="J81" s="56"/>
-      <c r="K81" s="56"/>
-      <c r="L81" s="56"/>
-      <c r="M81" s="56"/>
-      <c r="N81" s="56"/>
-      <c r="O81" s="56"/>
-      <c r="P81" s="56"/>
-      <c r="Q81" s="56"/>
-      <c r="R81" s="56"/>
-      <c r="S81" s="56"/>
-      <c r="T81" s="56"/>
-      <c r="U81" s="57"/>
+      <c r="E81" s="72"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="72"/>
+      <c r="H81" s="72"/>
+      <c r="I81" s="72"/>
+      <c r="J81" s="72"/>
+      <c r="K81" s="72"/>
+      <c r="L81" s="72"/>
+      <c r="M81" s="72"/>
+      <c r="N81" s="72"/>
+      <c r="O81" s="72"/>
+      <c r="P81" s="72"/>
+      <c r="Q81" s="72"/>
+      <c r="R81" s="72"/>
+      <c r="S81" s="72"/>
+      <c r="T81" s="72"/>
+      <c r="U81" s="73"/>
     </row>
     <row r="82" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="50"/>
+      <c r="A82" s="62"/>
       <c r="B82" s="47" t="s">
         <v>123</v>
       </c>
       <c r="C82" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="D82" s="58"/>
-      <c r="E82" s="59"/>
-      <c r="F82" s="59"/>
-      <c r="G82" s="59"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="59"/>
-      <c r="J82" s="59"/>
-      <c r="K82" s="59"/>
-      <c r="L82" s="59"/>
-      <c r="M82" s="59"/>
-      <c r="N82" s="59"/>
-      <c r="O82" s="59"/>
-      <c r="P82" s="59"/>
-      <c r="Q82" s="59"/>
-      <c r="R82" s="59"/>
-      <c r="S82" s="59"/>
-      <c r="T82" s="59"/>
-      <c r="U82" s="60"/>
+      <c r="D82" s="74"/>
+      <c r="E82" s="75"/>
+      <c r="F82" s="75"/>
+      <c r="G82" s="75"/>
+      <c r="H82" s="75"/>
+      <c r="I82" s="75"/>
+      <c r="J82" s="75"/>
+      <c r="K82" s="75"/>
+      <c r="L82" s="75"/>
+      <c r="M82" s="75"/>
+      <c r="N82" s="75"/>
+      <c r="O82" s="75"/>
+      <c r="P82" s="75"/>
+      <c r="Q82" s="75"/>
+      <c r="R82" s="75"/>
+      <c r="S82" s="75"/>
+      <c r="T82" s="75"/>
+      <c r="U82" s="76"/>
     </row>
     <row r="83" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="50"/>
+      <c r="A83" s="62"/>
       <c r="B83" s="47" t="s">
         <v>124</v>
       </c>
       <c r="C83" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="D83" s="58"/>
-      <c r="E83" s="59"/>
-      <c r="F83" s="59"/>
-      <c r="G83" s="59"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="59"/>
-      <c r="J83" s="59"/>
-      <c r="K83" s="59"/>
-      <c r="L83" s="59"/>
-      <c r="M83" s="59"/>
-      <c r="N83" s="59"/>
-      <c r="O83" s="59"/>
-      <c r="P83" s="59"/>
-      <c r="Q83" s="59"/>
-      <c r="R83" s="59"/>
-      <c r="S83" s="59"/>
-      <c r="T83" s="59"/>
-      <c r="U83" s="60"/>
+      <c r="D83" s="74"/>
+      <c r="E83" s="75"/>
+      <c r="F83" s="75"/>
+      <c r="G83" s="75"/>
+      <c r="H83" s="75"/>
+      <c r="I83" s="75"/>
+      <c r="J83" s="75"/>
+      <c r="K83" s="75"/>
+      <c r="L83" s="75"/>
+      <c r="M83" s="75"/>
+      <c r="N83" s="75"/>
+      <c r="O83" s="75"/>
+      <c r="P83" s="75"/>
+      <c r="Q83" s="75"/>
+      <c r="R83" s="75"/>
+      <c r="S83" s="75"/>
+      <c r="T83" s="75"/>
+      <c r="U83" s="76"/>
     </row>
     <row r="84" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="50"/>
+      <c r="A84" s="62"/>
       <c r="B84" s="47" t="s">
         <v>125</v>
       </c>
       <c r="C84" s="22" t="s">
         <v>35</v>
       </c>
-      <c r="D84" s="58"/>
-      <c r="E84" s="59"/>
-      <c r="F84" s="59"/>
-      <c r="G84" s="59"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="59"/>
-      <c r="J84" s="59"/>
-      <c r="K84" s="59"/>
-      <c r="L84" s="59"/>
-      <c r="M84" s="59"/>
-      <c r="N84" s="59"/>
-      <c r="O84" s="59"/>
-      <c r="P84" s="59"/>
-      <c r="Q84" s="59"/>
-      <c r="R84" s="59"/>
-      <c r="S84" s="59"/>
-      <c r="T84" s="59"/>
-      <c r="U84" s="60"/>
+      <c r="D84" s="74"/>
+      <c r="E84" s="75"/>
+      <c r="F84" s="75"/>
+      <c r="G84" s="75"/>
+      <c r="H84" s="75"/>
+      <c r="I84" s="75"/>
+      <c r="J84" s="75"/>
+      <c r="K84" s="75"/>
+      <c r="L84" s="75"/>
+      <c r="M84" s="75"/>
+      <c r="N84" s="75"/>
+      <c r="O84" s="75"/>
+      <c r="P84" s="75"/>
+      <c r="Q84" s="75"/>
+      <c r="R84" s="75"/>
+      <c r="S84" s="75"/>
+      <c r="T84" s="75"/>
+      <c r="U84" s="76"/>
     </row>
     <row r="85" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="50"/>
+      <c r="A85" s="62"/>
       <c r="B85" s="47" t="s">
         <v>126</v>
       </c>
       <c r="C85" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="D85" s="58"/>
-      <c r="E85" s="59"/>
-      <c r="F85" s="59"/>
-      <c r="G85" s="59"/>
-      <c r="H85" s="59"/>
-      <c r="I85" s="59"/>
-      <c r="J85" s="59"/>
-      <c r="K85" s="59"/>
-      <c r="L85" s="59"/>
-      <c r="M85" s="59"/>
-      <c r="N85" s="59"/>
-      <c r="O85" s="59"/>
-      <c r="P85" s="59"/>
-      <c r="Q85" s="59"/>
-      <c r="R85" s="59"/>
-      <c r="S85" s="59"/>
-      <c r="T85" s="59"/>
-      <c r="U85" s="60"/>
+      <c r="D85" s="74"/>
+      <c r="E85" s="75"/>
+      <c r="F85" s="75"/>
+      <c r="G85" s="75"/>
+      <c r="H85" s="75"/>
+      <c r="I85" s="75"/>
+      <c r="J85" s="75"/>
+      <c r="K85" s="75"/>
+      <c r="L85" s="75"/>
+      <c r="M85" s="75"/>
+      <c r="N85" s="75"/>
+      <c r="O85" s="75"/>
+      <c r="P85" s="75"/>
+      <c r="Q85" s="75"/>
+      <c r="R85" s="75"/>
+      <c r="S85" s="75"/>
+      <c r="T85" s="75"/>
+      <c r="U85" s="76"/>
     </row>
     <row r="86" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="50"/>
+      <c r="A86" s="62"/>
       <c r="B86" s="47" t="s">
         <v>127</v>
       </c>
       <c r="C86" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D86" s="58"/>
-      <c r="E86" s="59"/>
-      <c r="F86" s="59"/>
-      <c r="G86" s="59"/>
-      <c r="H86" s="59"/>
-      <c r="I86" s="59"/>
-      <c r="J86" s="59"/>
-      <c r="K86" s="59"/>
-      <c r="L86" s="59"/>
-      <c r="M86" s="59"/>
-      <c r="N86" s="59"/>
-      <c r="O86" s="59"/>
-      <c r="P86" s="59"/>
-      <c r="Q86" s="59"/>
-      <c r="R86" s="59"/>
-      <c r="S86" s="59"/>
-      <c r="T86" s="59"/>
-      <c r="U86" s="60"/>
+      <c r="D86" s="74"/>
+      <c r="E86" s="75"/>
+      <c r="F86" s="75"/>
+      <c r="G86" s="75"/>
+      <c r="H86" s="75"/>
+      <c r="I86" s="75"/>
+      <c r="J86" s="75"/>
+      <c r="K86" s="75"/>
+      <c r="L86" s="75"/>
+      <c r="M86" s="75"/>
+      <c r="N86" s="75"/>
+      <c r="O86" s="75"/>
+      <c r="P86" s="75"/>
+      <c r="Q86" s="75"/>
+      <c r="R86" s="75"/>
+      <c r="S86" s="75"/>
+      <c r="T86" s="75"/>
+      <c r="U86" s="76"/>
     </row>
     <row r="87" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="50"/>
+      <c r="A87" s="62"/>
       <c r="B87" s="47" t="s">
         <v>128</v>
       </c>
       <c r="C87" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D87" s="58"/>
-      <c r="E87" s="59"/>
-      <c r="F87" s="59"/>
-      <c r="G87" s="59"/>
-      <c r="H87" s="59"/>
-      <c r="I87" s="59"/>
-      <c r="J87" s="59"/>
-      <c r="K87" s="59"/>
-      <c r="L87" s="59"/>
-      <c r="M87" s="59"/>
-      <c r="N87" s="59"/>
-      <c r="O87" s="59"/>
-      <c r="P87" s="59"/>
-      <c r="Q87" s="59"/>
-      <c r="R87" s="59"/>
-      <c r="S87" s="59"/>
-      <c r="T87" s="59"/>
-      <c r="U87" s="60"/>
+      <c r="D87" s="74"/>
+      <c r="E87" s="75"/>
+      <c r="F87" s="75"/>
+      <c r="G87" s="75"/>
+      <c r="H87" s="75"/>
+      <c r="I87" s="75"/>
+      <c r="J87" s="75"/>
+      <c r="K87" s="75"/>
+      <c r="L87" s="75"/>
+      <c r="M87" s="75"/>
+      <c r="N87" s="75"/>
+      <c r="O87" s="75"/>
+      <c r="P87" s="75"/>
+      <c r="Q87" s="75"/>
+      <c r="R87" s="75"/>
+      <c r="S87" s="75"/>
+      <c r="T87" s="75"/>
+      <c r="U87" s="76"/>
     </row>
     <row r="88" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A88" s="54">
+      <c r="A88" s="52">
         <v>13</v>
       </c>
       <c r="B88" s="49" t="s">
@@ -14903,189 +14900,189 @@
       <c r="C88" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D88" s="58"/>
-      <c r="E88" s="59"/>
-      <c r="F88" s="59"/>
-      <c r="G88" s="59"/>
-      <c r="H88" s="59"/>
-      <c r="I88" s="59"/>
-      <c r="J88" s="59"/>
-      <c r="K88" s="59"/>
-      <c r="L88" s="59"/>
-      <c r="M88" s="59"/>
-      <c r="N88" s="59"/>
-      <c r="O88" s="59"/>
-      <c r="P88" s="59"/>
-      <c r="Q88" s="59"/>
-      <c r="R88" s="59"/>
-      <c r="S88" s="59"/>
-      <c r="T88" s="59"/>
-      <c r="U88" s="60"/>
+      <c r="D88" s="74"/>
+      <c r="E88" s="75"/>
+      <c r="F88" s="75"/>
+      <c r="G88" s="75"/>
+      <c r="H88" s="75"/>
+      <c r="I88" s="75"/>
+      <c r="J88" s="75"/>
+      <c r="K88" s="75"/>
+      <c r="L88" s="75"/>
+      <c r="M88" s="75"/>
+      <c r="N88" s="75"/>
+      <c r="O88" s="75"/>
+      <c r="P88" s="75"/>
+      <c r="Q88" s="75"/>
+      <c r="R88" s="75"/>
+      <c r="S88" s="75"/>
+      <c r="T88" s="75"/>
+      <c r="U88" s="76"/>
     </row>
     <row r="89" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A89" s="54"/>
+      <c r="A89" s="52"/>
       <c r="B89" s="49" t="s">
         <v>130</v>
       </c>
       <c r="C89" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D89" s="58"/>
-      <c r="E89" s="59"/>
-      <c r="F89" s="59"/>
-      <c r="G89" s="59"/>
-      <c r="H89" s="59"/>
-      <c r="I89" s="59"/>
-      <c r="J89" s="59"/>
-      <c r="K89" s="59"/>
-      <c r="L89" s="59"/>
-      <c r="M89" s="59"/>
-      <c r="N89" s="59"/>
-      <c r="O89" s="59"/>
-      <c r="P89" s="59"/>
-      <c r="Q89" s="59"/>
-      <c r="R89" s="59"/>
-      <c r="S89" s="59"/>
-      <c r="T89" s="59"/>
-      <c r="U89" s="60"/>
+      <c r="D89" s="74"/>
+      <c r="E89" s="75"/>
+      <c r="F89" s="75"/>
+      <c r="G89" s="75"/>
+      <c r="H89" s="75"/>
+      <c r="I89" s="75"/>
+      <c r="J89" s="75"/>
+      <c r="K89" s="75"/>
+      <c r="L89" s="75"/>
+      <c r="M89" s="75"/>
+      <c r="N89" s="75"/>
+      <c r="O89" s="75"/>
+      <c r="P89" s="75"/>
+      <c r="Q89" s="75"/>
+      <c r="R89" s="75"/>
+      <c r="S89" s="75"/>
+      <c r="T89" s="75"/>
+      <c r="U89" s="76"/>
     </row>
     <row r="90" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A90" s="54"/>
+      <c r="A90" s="52"/>
       <c r="B90" s="49" t="s">
         <v>131</v>
       </c>
       <c r="C90" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D90" s="58"/>
-      <c r="E90" s="59"/>
-      <c r="F90" s="59"/>
-      <c r="G90" s="59"/>
-      <c r="H90" s="59"/>
-      <c r="I90" s="59"/>
-      <c r="J90" s="59"/>
-      <c r="K90" s="59"/>
-      <c r="L90" s="59"/>
-      <c r="M90" s="59"/>
-      <c r="N90" s="59"/>
-      <c r="O90" s="59"/>
-      <c r="P90" s="59"/>
-      <c r="Q90" s="59"/>
-      <c r="R90" s="59"/>
-      <c r="S90" s="59"/>
-      <c r="T90" s="59"/>
-      <c r="U90" s="60"/>
+      <c r="D90" s="74"/>
+      <c r="E90" s="75"/>
+      <c r="F90" s="75"/>
+      <c r="G90" s="75"/>
+      <c r="H90" s="75"/>
+      <c r="I90" s="75"/>
+      <c r="J90" s="75"/>
+      <c r="K90" s="75"/>
+      <c r="L90" s="75"/>
+      <c r="M90" s="75"/>
+      <c r="N90" s="75"/>
+      <c r="O90" s="75"/>
+      <c r="P90" s="75"/>
+      <c r="Q90" s="75"/>
+      <c r="R90" s="75"/>
+      <c r="S90" s="75"/>
+      <c r="T90" s="75"/>
+      <c r="U90" s="76"/>
     </row>
     <row r="91" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="54"/>
+      <c r="A91" s="52"/>
       <c r="B91" s="49" t="s">
         <v>132</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="D91" s="58"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="59"/>
-      <c r="G91" s="59"/>
-      <c r="H91" s="59"/>
-      <c r="I91" s="59"/>
-      <c r="J91" s="59"/>
-      <c r="K91" s="59"/>
-      <c r="L91" s="59"/>
-      <c r="M91" s="59"/>
-      <c r="N91" s="59"/>
-      <c r="O91" s="59"/>
-      <c r="P91" s="59"/>
-      <c r="Q91" s="59"/>
-      <c r="R91" s="59"/>
-      <c r="S91" s="59"/>
-      <c r="T91" s="59"/>
-      <c r="U91" s="60"/>
+      <c r="D91" s="74"/>
+      <c r="E91" s="75"/>
+      <c r="F91" s="75"/>
+      <c r="G91" s="75"/>
+      <c r="H91" s="75"/>
+      <c r="I91" s="75"/>
+      <c r="J91" s="75"/>
+      <c r="K91" s="75"/>
+      <c r="L91" s="75"/>
+      <c r="M91" s="75"/>
+      <c r="N91" s="75"/>
+      <c r="O91" s="75"/>
+      <c r="P91" s="75"/>
+      <c r="Q91" s="75"/>
+      <c r="R91" s="75"/>
+      <c r="S91" s="75"/>
+      <c r="T91" s="75"/>
+      <c r="U91" s="76"/>
     </row>
     <row r="92" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A92" s="54"/>
+      <c r="A92" s="52"/>
       <c r="B92" s="49" t="s">
         <v>133</v>
       </c>
       <c r="C92" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="D92" s="58"/>
-      <c r="E92" s="59"/>
-      <c r="F92" s="59"/>
-      <c r="G92" s="59"/>
-      <c r="H92" s="59"/>
-      <c r="I92" s="59"/>
-      <c r="J92" s="59"/>
-      <c r="K92" s="59"/>
-      <c r="L92" s="59"/>
-      <c r="M92" s="59"/>
-      <c r="N92" s="59"/>
-      <c r="O92" s="59"/>
-      <c r="P92" s="59"/>
-      <c r="Q92" s="59"/>
-      <c r="R92" s="59"/>
-      <c r="S92" s="59"/>
-      <c r="T92" s="59"/>
-      <c r="U92" s="60"/>
+      <c r="D92" s="74"/>
+      <c r="E92" s="75"/>
+      <c r="F92" s="75"/>
+      <c r="G92" s="75"/>
+      <c r="H92" s="75"/>
+      <c r="I92" s="75"/>
+      <c r="J92" s="75"/>
+      <c r="K92" s="75"/>
+      <c r="L92" s="75"/>
+      <c r="M92" s="75"/>
+      <c r="N92" s="75"/>
+      <c r="O92" s="75"/>
+      <c r="P92" s="75"/>
+      <c r="Q92" s="75"/>
+      <c r="R92" s="75"/>
+      <c r="S92" s="75"/>
+      <c r="T92" s="75"/>
+      <c r="U92" s="76"/>
     </row>
     <row r="93" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A93" s="54"/>
+      <c r="A93" s="52"/>
       <c r="B93" s="49" t="s">
         <v>134</v>
       </c>
       <c r="C93" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="D93" s="58"/>
-      <c r="E93" s="59"/>
-      <c r="F93" s="59"/>
-      <c r="G93" s="59"/>
-      <c r="H93" s="59"/>
-      <c r="I93" s="59"/>
-      <c r="J93" s="59"/>
-      <c r="K93" s="59"/>
-      <c r="L93" s="59"/>
-      <c r="M93" s="59"/>
-      <c r="N93" s="59"/>
-      <c r="O93" s="59"/>
-      <c r="P93" s="59"/>
-      <c r="Q93" s="59"/>
-      <c r="R93" s="59"/>
-      <c r="S93" s="59"/>
-      <c r="T93" s="59"/>
-      <c r="U93" s="60"/>
+      <c r="D93" s="74"/>
+      <c r="E93" s="75"/>
+      <c r="F93" s="75"/>
+      <c r="G93" s="75"/>
+      <c r="H93" s="75"/>
+      <c r="I93" s="75"/>
+      <c r="J93" s="75"/>
+      <c r="K93" s="75"/>
+      <c r="L93" s="75"/>
+      <c r="M93" s="75"/>
+      <c r="N93" s="75"/>
+      <c r="O93" s="75"/>
+      <c r="P93" s="75"/>
+      <c r="Q93" s="75"/>
+      <c r="R93" s="75"/>
+      <c r="S93" s="75"/>
+      <c r="T93" s="75"/>
+      <c r="U93" s="76"/>
     </row>
     <row r="94" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A94" s="54"/>
+      <c r="A94" s="52"/>
       <c r="B94" s="49" t="s">
         <v>135</v>
       </c>
       <c r="C94" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="D94" s="61"/>
-      <c r="E94" s="62"/>
-      <c r="F94" s="62"/>
-      <c r="G94" s="62"/>
-      <c r="H94" s="62"/>
-      <c r="I94" s="62"/>
-      <c r="J94" s="62"/>
-      <c r="K94" s="62"/>
-      <c r="L94" s="62"/>
-      <c r="M94" s="62"/>
-      <c r="N94" s="62"/>
-      <c r="O94" s="62"/>
-      <c r="P94" s="62"/>
-      <c r="Q94" s="62"/>
-      <c r="R94" s="62"/>
-      <c r="S94" s="62"/>
-      <c r="T94" s="62"/>
-      <c r="U94" s="63"/>
+      <c r="D94" s="77"/>
+      <c r="E94" s="78"/>
+      <c r="F94" s="78"/>
+      <c r="G94" s="78"/>
+      <c r="H94" s="78"/>
+      <c r="I94" s="78"/>
+      <c r="J94" s="78"/>
+      <c r="K94" s="78"/>
+      <c r="L94" s="78"/>
+      <c r="M94" s="78"/>
+      <c r="N94" s="78"/>
+      <c r="O94" s="78"/>
+      <c r="P94" s="78"/>
+      <c r="Q94" s="78"/>
+      <c r="R94" s="78"/>
+      <c r="S94" s="78"/>
+      <c r="T94" s="78"/>
+      <c r="U94" s="79"/>
     </row>
     <row r="95" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="50">
+      <c r="A95" s="62">
         <v>14</v>
       </c>
       <c r="B95" s="47" t="s">
@@ -15118,7 +15115,7 @@
       <c r="U95" s="14"/>
     </row>
     <row r="96" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="50"/>
+      <c r="A96" s="62"/>
       <c r="B96" s="47" t="s">
         <v>138</v>
       </c>
@@ -15149,7 +15146,7 @@
       <c r="U96" s="14"/>
     </row>
     <row r="97" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="50"/>
+      <c r="A97" s="62"/>
       <c r="B97" s="47" t="s">
         <v>139</v>
       </c>
@@ -15180,7 +15177,7 @@
       <c r="U97" s="14"/>
     </row>
     <row r="98" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="50"/>
+      <c r="A98" s="62"/>
       <c r="B98" s="47" t="s">
         <v>140</v>
       </c>
@@ -15211,7 +15208,7 @@
       <c r="U98" s="14"/>
     </row>
     <row r="99" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="50"/>
+      <c r="A99" s="62"/>
       <c r="B99" s="47" t="s">
         <v>141</v>
       </c>
@@ -15242,7 +15239,7 @@
       <c r="U99" s="14"/>
     </row>
     <row r="100" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="50"/>
+      <c r="A100" s="62"/>
       <c r="B100" s="47" t="s">
         <v>142</v>
       </c>
@@ -15273,7 +15270,7 @@
       <c r="U100" s="14"/>
     </row>
     <row r="101" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="50"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="47" t="s">
         <v>143</v>
       </c>
@@ -15304,7 +15301,7 @@
       <c r="U101" s="14"/>
     </row>
     <row r="102" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="54">
+      <c r="A102" s="52">
         <v>15</v>
       </c>
       <c r="B102" s="49" t="s">
@@ -15337,7 +15334,7 @@
       <c r="U102" s="5"/>
     </row>
     <row r="103" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="54"/>
+      <c r="A103" s="52"/>
       <c r="B103" s="49" t="s">
         <v>145</v>
       </c>
@@ -15368,7 +15365,7 @@
       <c r="U103" s="5"/>
     </row>
     <row r="104" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="54"/>
+      <c r="A104" s="52"/>
       <c r="B104" s="49" t="s">
         <v>146</v>
       </c>
@@ -15399,7 +15396,7 @@
       <c r="U104" s="5"/>
     </row>
     <row r="105" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="54"/>
+      <c r="A105" s="52"/>
       <c r="B105" s="49" t="s">
         <v>147</v>
       </c>
@@ -15430,7 +15427,7 @@
       <c r="U105" s="5"/>
     </row>
     <row r="106" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="54"/>
+      <c r="A106" s="52"/>
       <c r="B106" s="49" t="s">
         <v>148</v>
       </c>
@@ -15461,7 +15458,7 @@
       <c r="U106" s="5"/>
     </row>
     <row r="107" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="54"/>
+      <c r="A107" s="52"/>
       <c r="B107" s="49" t="s">
         <v>149</v>
       </c>
@@ -15492,7 +15489,7 @@
       <c r="U107" s="5"/>
     </row>
     <row r="108" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="54"/>
+      <c r="A108" s="52"/>
       <c r="B108" s="49" t="s">
         <v>150</v>
       </c>
@@ -15523,7 +15520,7 @@
       <c r="U108" s="5"/>
     </row>
     <row r="109" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="50">
+      <c r="A109" s="62">
         <v>16</v>
       </c>
       <c r="B109" s="47" t="s">
@@ -15556,7 +15553,7 @@
       <c r="U109" s="15"/>
     </row>
     <row r="110" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A110" s="50"/>
+      <c r="A110" s="62"/>
       <c r="B110" s="47" t="s">
         <v>152</v>
       </c>
@@ -15587,7 +15584,7 @@
       <c r="U110" s="15"/>
     </row>
     <row r="111" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A111" s="50"/>
+      <c r="A111" s="62"/>
       <c r="B111" s="47" t="s">
         <v>153</v>
       </c>
@@ -15618,7 +15615,7 @@
       <c r="U111" s="15"/>
     </row>
     <row r="112" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A112" s="50"/>
+      <c r="A112" s="62"/>
       <c r="B112" s="47" t="s">
         <v>154</v>
       </c>
@@ -15649,7 +15646,7 @@
       <c r="U112" s="15"/>
     </row>
     <row r="113" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A113" s="50"/>
+      <c r="A113" s="62"/>
       <c r="B113" s="47" t="s">
         <v>155</v>
       </c>
@@ -15680,7 +15677,7 @@
       <c r="U113" s="15"/>
     </row>
     <row r="114" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A114" s="50"/>
+      <c r="A114" s="62"/>
       <c r="B114" s="47" t="s">
         <v>156</v>
       </c>
@@ -15711,7 +15708,7 @@
       <c r="U114" s="15"/>
     </row>
     <row r="115" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A115" s="50"/>
+      <c r="A115" s="62"/>
       <c r="B115" s="47" t="s">
         <v>157</v>
       </c>
@@ -15742,7 +15739,7 @@
       <c r="U115" s="15"/>
     </row>
     <row r="116" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="54">
+      <c r="A116" s="52">
         <v>17</v>
       </c>
       <c r="B116" s="49" t="s">
@@ -15775,7 +15772,7 @@
       <c r="U116" s="5"/>
     </row>
     <row r="117" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="54"/>
+      <c r="A117" s="52"/>
       <c r="B117" s="49" t="s">
         <v>159</v>
       </c>
@@ -15806,7 +15803,7 @@
       <c r="U117" s="5"/>
     </row>
     <row r="118" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="54"/>
+      <c r="A118" s="52"/>
       <c r="B118" s="49" t="s">
         <v>160</v>
       </c>
@@ -15837,7 +15834,7 @@
       <c r="U118" s="5"/>
     </row>
     <row r="119" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="54"/>
+      <c r="A119" s="52"/>
       <c r="B119" s="49" t="s">
         <v>161</v>
       </c>
@@ -15868,7 +15865,7 @@
       <c r="U119" s="5"/>
     </row>
     <row r="120" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="54"/>
+      <c r="A120" s="52"/>
       <c r="B120" s="49" t="s">
         <v>162</v>
       </c>
@@ -15899,7 +15896,7 @@
       <c r="U120" s="5"/>
     </row>
     <row r="121" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="54"/>
+      <c r="A121" s="52"/>
       <c r="B121" s="49" t="s">
         <v>163</v>
       </c>
@@ -15930,7 +15927,7 @@
       <c r="U121" s="5"/>
     </row>
     <row r="122" spans="1:21" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="54"/>
+      <c r="A122" s="52"/>
       <c r="B122" s="49" t="s">
         <v>164</v>
       </c>
@@ -15961,7 +15958,7 @@
       <c r="U122" s="5"/>
     </row>
     <row r="123" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A123" s="50">
+      <c r="A123" s="62">
         <v>18</v>
       </c>
       <c r="B123" s="47" t="s">
@@ -15994,7 +15991,7 @@
       <c r="U123" s="15"/>
     </row>
     <row r="124" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A124" s="50"/>
+      <c r="A124" s="62"/>
       <c r="B124" s="47" t="s">
         <v>166</v>
       </c>
@@ -16025,7 +16022,7 @@
       <c r="U124" s="15"/>
     </row>
     <row r="125" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A125" s="50"/>
+      <c r="A125" s="62"/>
       <c r="B125" s="47" t="s">
         <v>167</v>
       </c>
@@ -16056,7 +16053,7 @@
       <c r="U125" s="15"/>
     </row>
     <row r="126" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A126" s="50"/>
+      <c r="A126" s="62"/>
       <c r="B126" s="47" t="s">
         <v>168</v>
       </c>
@@ -16087,36 +16084,36 @@
       <c r="U126" s="15"/>
     </row>
     <row r="127" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A127" s="50"/>
+      <c r="A127" s="62"/>
       <c r="B127" s="46" t="s">
         <v>169</v>
       </c>
       <c r="C127" s="39" t="s">
         <v>40</v>
       </c>
-      <c r="D127" s="51" t="s">
+      <c r="D127" s="68" t="s">
         <v>170</v>
       </c>
-      <c r="E127" s="52"/>
-      <c r="F127" s="52"/>
-      <c r="G127" s="52"/>
-      <c r="H127" s="52"/>
-      <c r="I127" s="52"/>
-      <c r="J127" s="52"/>
-      <c r="K127" s="52"/>
-      <c r="L127" s="52"/>
-      <c r="M127" s="52"/>
-      <c r="N127" s="52"/>
-      <c r="O127" s="52"/>
-      <c r="P127" s="52"/>
-      <c r="Q127" s="52"/>
-      <c r="R127" s="52"/>
-      <c r="S127" s="52"/>
-      <c r="T127" s="52"/>
-      <c r="U127" s="53"/>
+      <c r="E127" s="69"/>
+      <c r="F127" s="69"/>
+      <c r="G127" s="69"/>
+      <c r="H127" s="69"/>
+      <c r="I127" s="69"/>
+      <c r="J127" s="69"/>
+      <c r="K127" s="69"/>
+      <c r="L127" s="69"/>
+      <c r="M127" s="69"/>
+      <c r="N127" s="69"/>
+      <c r="O127" s="69"/>
+      <c r="P127" s="69"/>
+      <c r="Q127" s="69"/>
+      <c r="R127" s="69"/>
+      <c r="S127" s="69"/>
+      <c r="T127" s="69"/>
+      <c r="U127" s="70"/>
     </row>
     <row r="128" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A128" s="50"/>
+      <c r="A128" s="62"/>
       <c r="B128" s="47" t="s">
         <v>171</v>
       </c>
@@ -16147,7 +16144,7 @@
       <c r="U128" s="15"/>
     </row>
     <row r="129" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A129" s="50"/>
+      <c r="A129" s="62"/>
       <c r="B129" s="47" t="s">
         <v>172</v>
       </c>
@@ -16178,7 +16175,7 @@
       <c r="U129" s="15"/>
     </row>
     <row r="130" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A130" s="54">
+      <c r="A130" s="52">
         <v>19</v>
       </c>
       <c r="B130" s="49" t="s">
@@ -16211,7 +16208,7 @@
       <c r="U130" s="5"/>
     </row>
     <row r="131" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A131" s="54"/>
+      <c r="A131" s="52"/>
       <c r="B131" s="49" t="s">
         <v>174</v>
       </c>
@@ -16242,7 +16239,7 @@
       <c r="U131" s="5"/>
     </row>
     <row r="132" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A132" s="54"/>
+      <c r="A132" s="52"/>
       <c r="B132" s="49" t="s">
         <v>175</v>
       </c>
@@ -16273,7 +16270,7 @@
       <c r="U132" s="5"/>
     </row>
     <row r="133" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A133" s="54"/>
+      <c r="A133" s="52"/>
       <c r="B133" s="49" t="s">
         <v>176</v>
       </c>
@@ -16304,7 +16301,7 @@
       <c r="U133" s="5"/>
     </row>
     <row r="134" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A134" s="54"/>
+      <c r="A134" s="52"/>
       <c r="B134" s="49" t="s">
         <v>177</v>
       </c>
@@ -16335,7 +16332,7 @@
       <c r="U134" s="5"/>
     </row>
     <row r="135" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A135" s="54"/>
+      <c r="A135" s="52"/>
       <c r="B135" s="49" t="s">
         <v>178</v>
       </c>
@@ -16366,7 +16363,7 @@
       <c r="U135" s="5"/>
     </row>
     <row r="136" spans="1:21" s="7" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A136" s="54"/>
+      <c r="A136" s="52"/>
       <c r="B136" s="49" t="s">
         <v>179</v>
       </c>
@@ -16412,6 +16409,27 @@
     <row r="150" ht="20.25"/>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="A123:A129"/>
+    <mergeCell ref="D127:U127"/>
+    <mergeCell ref="A130:A136"/>
+    <mergeCell ref="D81:U94"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A101"/>
+    <mergeCell ref="A102:A108"/>
+    <mergeCell ref="A109:A115"/>
+    <mergeCell ref="A116:A122"/>
+    <mergeCell ref="A81:A87"/>
+    <mergeCell ref="A46:A52"/>
+    <mergeCell ref="A53:A59"/>
+    <mergeCell ref="A60:A66"/>
+    <mergeCell ref="A67:A73"/>
+    <mergeCell ref="A74:A80"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="D29:U31"/>
     <mergeCell ref="M2:O2"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="D35:U41"/>
@@ -16428,27 +16446,6 @@
     <mergeCell ref="B2:C3"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A17"/>
-    <mergeCell ref="A18:A24"/>
-    <mergeCell ref="A25:A31"/>
-    <mergeCell ref="D29:U31"/>
-    <mergeCell ref="A46:A52"/>
-    <mergeCell ref="A53:A59"/>
-    <mergeCell ref="A60:A66"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A74:A80"/>
-    <mergeCell ref="A123:A129"/>
-    <mergeCell ref="D127:U127"/>
-    <mergeCell ref="A130:A136"/>
-    <mergeCell ref="D81:U94"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A101"/>
-    <mergeCell ref="A102:A108"/>
-    <mergeCell ref="A109:A115"/>
-    <mergeCell ref="A116:A122"/>
-    <mergeCell ref="A81:A87"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
